--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>46204</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>45114</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45106</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>45590</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45061</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>45063</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>45660</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>43955</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45659</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>46132</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>46132</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45439</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>46030</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>45106</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 37798-2026</t>
+          <t>A 26552-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46279</v>
+        <v>46183</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2670,45 +2670,186 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>22.4</v>
+        <v>3.2</v>
       </c>
       <c r="J16" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
       </c>
       <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
         <v>2</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
+        <v>24</v>
+      </c>
+      <c r="T16" t="n">
+        <v>97</v>
+      </c>
+      <c r="U16" t="n">
+        <v>96</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Knärot
+Dropptaggsvamp
+Fjällig taggsvamp s.str.
+Sårläka
+Vårärt
+Granbarkgnagare
+Grön sköldmossa
+Grönpyrola
+Skogsknipprot
+Stor aspticka
+Stubbspretmossa
+Stuplav
+Tibast
+Tvåblad
+Blåsippa
+Brudborste
+Ekbräken
+Kransmossa
+Ormbär
+Spillkråka
+Tofsmes
+Nattviol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0382/artfynd/A 26552-2026 artfynd.xlsx", "A 26552-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0382/kartor/A 26552-2026 karta.png", "A 26552-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0382/kartor_geotiff/A 26552-2026 georefererad karta.tif", "A 26552-2026")</f>
+        <v/>
+      </c>
+      <c r="Z16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0382/knärot/A 26552-2026 karta knärot.png", "A 26552-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0382/klagomål/A 26552-2026 FSC-klagomål.docx", "A 26552-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0382/klagomålsmail/A 26552-2026 FSC-klagomål mail.docx", "A 26552-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0382/tillsyn/A 26552-2026 tillsynsbegäran.docx", "A 26552-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0382/tillsynsmail/A 26552-2026 tillsynsbegäran mail.docx", "A 26552-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0382/fåglar/A 26552-2026 prioriterade fågelarter.docx", "A 26552-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 37798-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖSTHAMMAR</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>18</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>13</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>16</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>3</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>23</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>41</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsalm
@@ -2735,116 +2876,116 @@
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/artfynd/A 37798-2026 artfynd.xlsx", "A 37798-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/kartor/A 37798-2026 karta.png", "A 37798-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/kartor_geotiff/A 37798-2026 georefererad karta.tif", "A 37798-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/klagomål/A 37798-2026 FSC-klagomål.docx", "A 37798-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/klagomålsmail/A 37798-2026 FSC-klagomål mail.docx", "A 37798-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/tillsyn/A 37798-2026 tillsynsbegäran.docx", "A 37798-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/tillsynsmail/A 37798-2026 tillsynsbegäran mail.docx", "A 37798-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/fåglar/A 37798-2026 prioriterade fågelarter.docx", "A 37798-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>S 3125-2023</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>45182</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖSTHAMMAR</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ÖSTHAMMAR</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Bergvik skog öst AB</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>13.2</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>20</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" t="n">
         <v>3</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" t="n">
         <v>6</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M18" t="n">
         <v>3</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N18" t="n">
         <v>2</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>11</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>5</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>23</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>32</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>2</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Ask
 Större agatsnäcka
@@ -2871,175 +3012,36 @@
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/artfynd/S 3125-2023 artfynd.xlsx", "S 3125-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/kartor/S 3125-2023 karta.png", "S 3125-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/kartor_geotiff/S 3125-2023 georefererad karta.tif", "S 3125-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/klagomål/S 3125-2023 FSC-klagomål.docx", "S 3125-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/klagomålsmail/S 3125-2023 FSC-klagomål mail.docx", "S 3125-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/tillsyn/S 3125-2023 tillsynsbegäran.docx", "S 3125-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/tillsynsmail/S 3125-2023 tillsynsbegäran mail.docx", "S 3125-2023")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0382/fåglar/S 3125-2023 prioriterade fågelarter.docx", "S 3125-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 26552-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ÖSTHAMMAR</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>9</v>
-      </c>
-      <c r="K18" t="n">
-        <v>9</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>22</v>
-      </c>
-      <c r="T18" t="n">
-        <v>94</v>
-      </c>
-      <c r="U18" t="n">
-        <v>93</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Knärot
-Sårläka
-Vårärt
-Granbarkgnagare
-Grön sköldmossa
-Grönpyrola
-Skogsknipprot
-Stor aspticka
-Stubbspretmossa
-Stuplav
-Tibast
-Tvåblad
-Blåsippa
-Brudborste
-Ekbräken
-Kransmossa
-Ormbär
-Spillkråka
-Tofsmes
-Nattviol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0382/artfynd/A 26552-2026 artfynd.xlsx", "A 26552-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0382/kartor/A 26552-2026 karta.png", "A 26552-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0382/kartor_geotiff/A 26552-2026 georefererad karta.tif", "A 26552-2026")</f>
-        <v/>
-      </c>
-      <c r="Z18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0382/knärot/A 26552-2026 karta knärot.png", "A 26552-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0382/klagomål/A 26552-2026 FSC-klagomål.docx", "A 26552-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0382/klagomålsmail/A 26552-2026 FSC-klagomål mail.docx", "A 26552-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0382/tillsyn/A 26552-2026 tillsynsbegäran.docx", "A 26552-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0382/tillsynsmail/A 26552-2026 tillsynsbegäran mail.docx", "A 26552-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0382/fåglar/A 26552-2026 prioriterade fågelarter.docx", "A 26552-2026")</f>
         <v/>
       </c>
     </row>
@@ -3063,7 +3065,7 @@
         <v>46205</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3202,7 +3204,7 @@
         <v>44918</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3332,7 +3334,7 @@
         <v>45182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3467,7 +3469,7 @@
         <v>46009</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3605,7 +3607,7 @@
         <v>46196</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3738,7 +3740,7 @@
         <v>45210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3861,7 +3863,7 @@
         <v>44865</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3990,7 +3992,7 @@
         <v>45681</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4122,7 +4124,7 @@
         <v>46132</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4248,7 +4250,7 @@
         <v>44662</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4368,7 +4370,7 @@
         <v>44482</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4483,7 +4485,7 @@
         <v>45660</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4607,7 +4609,7 @@
         <v>45622</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4735,7 +4737,7 @@
         <v>44938</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4858,7 +4860,7 @@
         <v>45076</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4982,7 +4984,7 @@
         <v>44771</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5096,7 +5098,7 @@
         <v>45947</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5219,7 +5221,7 @@
         <v>45190</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5342,7 +5344,7 @@
         <v>46205</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5469,7 +5471,7 @@
         <v>44935</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5583,7 +5585,7 @@
         <v>45796</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5706,7 +5708,7 @@
         <v>44644</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5819,7 +5821,7 @@
         <v>45226</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5945,7 +5947,7 @@
         <v>45891</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6071,7 +6073,7 @@
         <v>44194</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6188,7 +6190,7 @@
         <v>45076</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6309,7 +6311,7 @@
         <v>44636</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6421,7 +6423,7 @@
         <v>46170</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6537,7 +6539,7 @@
         <v>44474</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6653,7 +6655,7 @@
         <v>45840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6764,7 +6766,7 @@
         <v>44837</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6884,7 +6886,7 @@
         <v>45362</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6999,7 +7001,7 @@
         <v>46071</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7110,7 +7112,7 @@
         <v>45198</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7221,7 +7223,7 @@
         <v>45160</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7337,7 +7339,7 @@
         <v>44588</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7457,7 +7459,7 @@
         <v>44779</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7575,7 +7577,7 @@
         <v>44739</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7689,7 +7691,7 @@
         <v>45238</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7803,7 +7805,7 @@
         <v>44727</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7913,7 +7915,7 @@
         <v>45205</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8023,7 +8025,7 @@
         <v>44819</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8136,7 +8138,7 @@
         <v>44511</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8249,7 +8251,7 @@
         <v>44684</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8366,7 +8368,7 @@
         <v>44874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8484,7 +8486,7 @@
         <v>44728</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8602,7 +8604,7 @@
         <v>45078</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8711,7 +8713,7 @@
         <v>44525</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8820,7 +8822,7 @@
         <v>45107</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8934,7 +8936,7 @@
         <v>46265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9043,7 +9045,7 @@
         <v>45412</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9157,7 +9159,7 @@
         <v>45315</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9271,7 +9273,7 @@
         <v>45070</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9379,7 +9381,7 @@
         <v>44984</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9487,7 +9489,7 @@
         <v>45999</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9595,7 +9597,7 @@
         <v>45520</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9712,7 +9714,7 @@
         <v>46048</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9820,7 +9822,7 @@
         <v>44858</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9928,7 +9930,7 @@
         <v>45545</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10036,7 +10038,7 @@
         <v>45699</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10149,7 +10151,7 @@
         <v>45390</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10262,7 +10264,7 @@
         <v>44874</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10378,7 +10380,7 @@
         <v>45372</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10485,7 +10487,7 @@
         <v>44903</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10592,7 +10594,7 @@
         <v>46161</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10704,7 +10706,7 @@
         <v>45999</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10811,7 +10813,7 @@
         <v>44555</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10918,7 +10920,7 @@
         <v>44683</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11025,7 +11027,7 @@
         <v>46121</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11132,7 +11134,7 @@
         <v>44729</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11243,7 +11245,7 @@
         <v>45446</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11355,7 +11357,7 @@
         <v>45460</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11467,7 +11469,7 @@
         <v>45274</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11574,7 +11576,7 @@
         <v>45895</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11681,7 +11683,7 @@
         <v>46089</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11793,7 +11795,7 @@
         <v>44495</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11899,7 +11901,7 @@
         <v>44515</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12018,7 +12020,7 @@
         <v>44578</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12124,7 +12126,7 @@
         <v>44778</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12230,7 +12232,7 @@
         <v>45068</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12336,7 +12338,7 @@
         <v>45045</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12447,7 +12449,7 @@
         <v>45425</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12553,7 +12555,7 @@
         <v>45775</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12659,7 +12661,7 @@
         <v>45583</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12770,7 +12772,7 @@
         <v>44644</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12876,7 +12878,7 @@
         <v>46142</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12987,7 +12989,7 @@
         <v>45951</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13098,7 +13100,7 @@
         <v>46001</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13209,7 +13211,7 @@
         <v>45743</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13315,7 +13317,7 @@
         <v>45063</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13426,7 +13428,7 @@
         <v>44883</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13532,7 +13534,7 @@
         <v>45063</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13643,7 +13645,7 @@
         <v>46252</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13758,7 +13760,7 @@
         <v>45393</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13864,7 +13866,7 @@
         <v>44782</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13970,7 +13972,7 @@
         <v>44859</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14085,7 +14087,7 @@
         <v>44687</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14190,7 +14192,7 @@
         <v>44813</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14300,7 +14302,7 @@
         <v>44622</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14410,7 +14412,7 @@
         <v>44501</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14520,7 +14522,7 @@
         <v>44792</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14625,7 +14627,7 @@
         <v>44715</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14730,7 +14732,7 @@
         <v>44606</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14835,7 +14837,7 @@
         <v>45154</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14945,7 +14947,7 @@
         <v>45329</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15050,7 +15052,7 @@
         <v>45678</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15155,7 +15157,7 @@
         <v>45896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15265,7 +15267,7 @@
         <v>45831</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15370,7 +15372,7 @@
         <v>44985</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15475,7 +15477,7 @@
         <v>46139</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15584,7 +15586,7 @@
         <v>45695</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15693,7 +15695,7 @@
         <v>44607</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15798,7 +15800,7 @@
         <v>44712</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15908,7 +15910,7 @@
         <v>45384</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16013,7 +16015,7 @@
         <v>45160</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16118,7 +16120,7 @@
         <v>45436</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16223,7 +16225,7 @@
         <v>44915</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16328,7 +16330,7 @@
         <v>46154</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16438,7 +16440,7 @@
         <v>45013</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16543,7 +16545,7 @@
         <v>44572</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16648,7 +16650,7 @@
         <v>44991</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16753,7 +16755,7 @@
         <v>44875</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16858,7 +16860,7 @@
         <v>45162</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16968,7 +16970,7 @@
         <v>46056</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17078,7 +17080,7 @@
         <v>45156</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17183,7 +17185,7 @@
         <v>46062</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17288,7 +17290,7 @@
         <v>45387</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17393,7 +17395,7 @@
         <v>46098</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17498,7 +17500,7 @@
         <v>44979</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17608,7 +17610,7 @@
         <v>46195</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17718,7 +17720,7 @@
         <v>46195</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17832,7 +17834,7 @@
         <v>44998</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17937,7 +17939,7 @@
         <v>44517</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18042,7 +18044,7 @@
         <v>46063</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18147,7 +18149,7 @@
         <v>45078</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18257,7 +18259,7 @@
         <v>46211</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18367,7 +18369,7 @@
         <v>46211</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18477,7 +18479,7 @@
         <v>46259</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18587,7 +18589,7 @@
         <v>46002</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18697,7 +18699,7 @@
         <v>45250</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18802,7 +18804,7 @@
         <v>45135</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18916,7 +18918,7 @@
         <v>46260</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19026,7 +19028,7 @@
         <v>45007</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19131,7 +19133,7 @@
         <v>45213</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19236,7 +19238,7 @@
         <v>46268</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19350,7 +19352,7 @@
         <v>45513</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19460,7 +19462,7 @@
         <v>46275</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19565,7 +19567,7 @@
         <v>44509</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19670,7 +19672,7 @@
         <v>46235</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19780,7 +19782,7 @@
         <v>45078</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19885,7 +19887,7 @@
         <v>45218</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19990,7 +19992,7 @@
         <v>45178</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20100,7 +20102,7 @@
         <v>45007</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20205,7 +20207,7 @@
         <v>44726</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20310,7 +20312,7 @@
         <v>44491</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20415,7 +20417,7 @@
         <v>45078</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20520,7 +20522,7 @@
         <v>44610</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20625,7 +20627,7 @@
         <v>45820</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20730,7 +20732,7 @@
         <v>45728</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20835,7 +20837,7 @@
         <v>46112</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20940,7 +20942,7 @@
         <v>46191</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21045,7 +21047,7 @@
         <v>44555</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21118,7 +21120,7 @@
         <v>44729</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21196,7 +21198,7 @@
         <v>44732</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21269,7 +21271,7 @@
         <v>44614</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21342,7 +21344,7 @@
         <v>44622</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21420,7 +21422,7 @@
         <v>44501</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21498,7 +21500,7 @@
         <v>44622</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21576,7 +21578,7 @@
         <v>44687</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21649,7 +21651,7 @@
         <v>44664</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21722,7 +21724,7 @@
         <v>44651</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21800,7 +21802,7 @@
         <v>44644</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21873,7 +21875,7 @@
         <v>44868</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21946,7 +21948,7 @@
         <v>44498</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22019,7 +22021,7 @@
         <v>44491</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22097,7 +22099,7 @@
         <v>44838</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22175,7 +22177,7 @@
         <v>44691</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22248,7 +22250,7 @@
         <v>44577</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22326,7 +22328,7 @@
         <v>44461</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22399,7 +22401,7 @@
         <v>44525</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22472,7 +22474,7 @@
         <v>44661</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22550,7 +22552,7 @@
         <v>44649</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22628,7 +22630,7 @@
         <v>44622</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22706,7 +22708,7 @@
         <v>44613</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22779,7 +22781,7 @@
         <v>44588</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22857,7 +22859,7 @@
         <v>44725</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22930,7 +22932,7 @@
         <v>44852</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23003,7 +23005,7 @@
         <v>44725</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23076,7 +23078,7 @@
         <v>44519</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -23154,7 +23156,7 @@
         <v>44598</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -23232,7 +23234,7 @@
         <v>44692</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -23310,7 +23312,7 @@
         <v>44462</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23383,7 +23385,7 @@
         <v>44691</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23456,7 +23458,7 @@
         <v>44694</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23534,7 +23536,7 @@
         <v>44659</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23607,7 +23609,7 @@
         <v>44865</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23685,7 +23687,7 @@
         <v>44715</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23763,7 +23765,7 @@
         <v>44664</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23836,7 +23838,7 @@
         <v>44757</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23914,7 +23916,7 @@
         <v>44861</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23987,7 +23989,7 @@
         <v>44873</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -24060,7 +24062,7 @@
         <v>44661</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -24138,7 +24140,7 @@
         <v>44809</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -24211,7 +24213,7 @@
         <v>44501</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -24289,7 +24291,7 @@
         <v>44809</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24362,7 +24364,7 @@
         <v>44813</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24440,7 +24442,7 @@
         <v>44810</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24513,7 +24515,7 @@
         <v>44712</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24591,7 +24593,7 @@
         <v>44635</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24669,7 +24671,7 @@
         <v>44669</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24747,7 +24749,7 @@
         <v>44687</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24825,7 +24827,7 @@
         <v>44608</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24898,7 +24900,7 @@
         <v>44728</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24976,7 +24978,7 @@
         <v>44872</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -25049,7 +25051,7 @@
         <v>44770</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -25127,7 +25129,7 @@
         <v>44739</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -25205,7 +25207,7 @@
         <v>44467</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -25278,7 +25280,7 @@
         <v>44620</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -25351,7 +25353,7 @@
         <v>44687</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25429,7 +25431,7 @@
         <v>44635</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25502,7 +25504,7 @@
         <v>44676</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25580,7 +25582,7 @@
         <v>44643</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25653,7 +25655,7 @@
         <v>44669</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25731,7 +25733,7 @@
         <v>44466</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25809,7 +25811,7 @@
         <v>44482</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25882,7 +25884,7 @@
         <v>44809</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25955,7 +25957,7 @@
         <v>45114</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -26033,7 +26035,7 @@
         <v>44560</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -26111,7 +26113,7 @@
         <v>45208</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -26184,7 +26186,7 @@
         <v>44775</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -26257,7 +26259,7 @@
         <v>44991</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -26330,7 +26332,7 @@
         <v>45621</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26408,7 +26410,7 @@
         <v>45271</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26481,7 +26483,7 @@
         <v>45107</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26559,7 +26561,7 @@
         <v>44591</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26637,7 +26639,7 @@
         <v>45054</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26710,7 +26712,7 @@
         <v>45110</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26783,7 +26785,7 @@
         <v>44755</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26856,7 +26858,7 @@
         <v>44783</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26934,7 +26936,7 @@
         <v>45212</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -27012,7 +27014,7 @@
         <v>45191</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -27090,7 +27092,7 @@
         <v>44915</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -27163,7 +27165,7 @@
         <v>44651</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -27241,7 +27243,7 @@
         <v>44643</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -27319,7 +27321,7 @@
         <v>44599</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27392,7 +27394,7 @@
         <v>44599</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27465,7 +27467,7 @@
         <v>44576</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27543,7 +27545,7 @@
         <v>44706</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27616,7 +27618,7 @@
         <v>45146</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27694,7 +27696,7 @@
         <v>44651</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27772,7 +27774,7 @@
         <v>45250</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27845,7 +27847,7 @@
         <v>44860</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27918,7 +27920,7 @@
         <v>44987</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27991,7 +27993,7 @@
         <v>44768</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -28069,7 +28071,7 @@
         <v>45230</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -28142,7 +28144,7 @@
         <v>44814</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -28215,7 +28217,7 @@
         <v>45670</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -28288,7 +28290,7 @@
         <v>45162</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -28366,7 +28368,7 @@
         <v>44963</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28439,7 +28441,7 @@
         <v>44746</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28512,7 +28514,7 @@
         <v>45257</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28585,7 +28587,7 @@
         <v>45194</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28663,7 +28665,7 @@
         <v>44991</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28741,7 +28743,7 @@
         <v>45516</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28814,7 +28816,7 @@
         <v>44511</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28887,7 +28889,7 @@
         <v>44533</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28965,7 +28967,7 @@
         <v>45063</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -29043,7 +29045,7 @@
         <v>45561</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -29121,7 +29123,7 @@
         <v>44555</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29194,7 +29196,7 @@
         <v>45455</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -29272,7 +29274,7 @@
         <v>44515</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -29350,7 +29352,7 @@
         <v>45337</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29423,7 +29425,7 @@
         <v>45544</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29501,7 +29503,7 @@
         <v>44572</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29574,7 +29576,7 @@
         <v>44770</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29652,7 +29654,7 @@
         <v>45462</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29725,7 +29727,7 @@
         <v>45212</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29803,7 +29805,7 @@
         <v>44560</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29881,7 +29883,7 @@
         <v>45530</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29959,7 +29961,7 @@
         <v>45419</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30032,7 +30034,7 @@
         <v>44970</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -30105,7 +30107,7 @@
         <v>44953</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -30178,7 +30180,7 @@
         <v>45152</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -30251,7 +30253,7 @@
         <v>45093</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -30329,7 +30331,7 @@
         <v>45379</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30407,7 +30409,7 @@
         <v>45358</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30485,7 +30487,7 @@
         <v>45520</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30563,7 +30565,7 @@
         <v>44664</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30636,7 +30638,7 @@
         <v>45075</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30709,7 +30711,7 @@
         <v>44613</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30782,7 +30784,7 @@
         <v>44643</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30855,7 +30857,7 @@
         <v>45757</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30933,7 +30935,7 @@
         <v>45520</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -31011,7 +31013,7 @@
         <v>44613</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -31084,7 +31086,7 @@
         <v>45225</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -31157,7 +31159,7 @@
         <v>45148</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31235,7 +31237,7 @@
         <v>45244</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -31308,7 +31310,7 @@
         <v>45341</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31381,7 +31383,7 @@
         <v>44496</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31454,7 +31456,7 @@
         <v>45102</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31532,7 +31534,7 @@
         <v>45102</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31610,7 +31612,7 @@
         <v>45572</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31683,7 +31685,7 @@
         <v>44894</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31756,7 +31758,7 @@
         <v>45202</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31829,7 +31831,7 @@
         <v>45384</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31902,7 +31904,7 @@
         <v>46139</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31975,7 +31977,7 @@
         <v>44963</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -32048,7 +32050,7 @@
         <v>44874</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -32121,7 +32123,7 @@
         <v>45337</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32194,7 +32196,7 @@
         <v>44896</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32267,7 +32269,7 @@
         <v>44896</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -32340,7 +32342,7 @@
         <v>46139</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32413,7 +32415,7 @@
         <v>45975</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32486,7 +32488,7 @@
         <v>44461</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32559,7 +32561,7 @@
         <v>46034</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32632,7 +32634,7 @@
         <v>45187</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32710,7 +32712,7 @@
         <v>46034</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32783,7 +32785,7 @@
         <v>45102</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32861,7 +32863,7 @@
         <v>46136</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32934,7 +32936,7 @@
         <v>45805</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -33007,7 +33009,7 @@
         <v>45233</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -33085,7 +33087,7 @@
         <v>45516</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -33163,7 +33165,7 @@
         <v>45895</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33236,7 +33238,7 @@
         <v>45895</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -33309,7 +33311,7 @@
         <v>45895</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33382,7 +33384,7 @@
         <v>45895</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33455,7 +33457,7 @@
         <v>45760</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33533,7 +33535,7 @@
         <v>44959</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33611,7 +33613,7 @@
         <v>44991</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33689,7 +33691,7 @@
         <v>44495</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33767,7 +33769,7 @@
         <v>45895</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33840,7 +33842,7 @@
         <v>44950</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33918,7 +33920,7 @@
         <v>44512</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33991,7 +33993,7 @@
         <v>45898</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -34069,7 +34071,7 @@
         <v>45079</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -34142,7 +34144,7 @@
         <v>45519</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34220,7 +34222,7 @@
         <v>45733</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34293,7 +34295,7 @@
         <v>44725</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -34366,7 +34368,7 @@
         <v>45433</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34439,7 +34441,7 @@
         <v>45840</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34512,7 +34514,7 @@
         <v>45797</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34585,7 +34587,7 @@
         <v>45797</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34658,7 +34660,7 @@
         <v>45797</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34731,7 +34733,7 @@
         <v>45817</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34809,7 +34811,7 @@
         <v>45909</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34882,7 +34884,7 @@
         <v>44928</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34955,7 +34957,7 @@
         <v>44928</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -35028,7 +35030,7 @@
         <v>45621</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -35106,7 +35108,7 @@
         <v>45520</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35184,7 +35186,7 @@
         <v>46104</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35262,7 +35264,7 @@
         <v>45112</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35340,7 +35342,7 @@
         <v>46141</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35418,7 +35420,7 @@
         <v>46141</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35496,7 +35498,7 @@
         <v>46104</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35574,7 +35576,7 @@
         <v>44476</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35652,7 +35654,7 @@
         <v>45063</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35725,7 +35727,7 @@
         <v>45646</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35798,7 +35800,7 @@
         <v>44687</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35871,7 +35873,7 @@
         <v>45362</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35944,7 +35946,7 @@
         <v>45924</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -36017,7 +36019,7 @@
         <v>45102</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -36095,7 +36097,7 @@
         <v>45496</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36173,7 +36175,7 @@
         <v>44591</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36246,7 +36248,7 @@
         <v>45230</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36319,7 +36321,7 @@
         <v>45174</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36397,7 +36399,7 @@
         <v>45040</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36470,7 +36472,7 @@
         <v>45090</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36548,7 +36550,7 @@
         <v>45218</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36621,7 +36623,7 @@
         <v>45239</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36694,7 +36696,7 @@
         <v>45044</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36767,7 +36769,7 @@
         <v>45931</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36840,7 +36842,7 @@
         <v>44905</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36913,7 +36915,7 @@
         <v>45755</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36991,7 +36993,7 @@
         <v>45482</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -37069,7 +37071,7 @@
         <v>46147</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -37142,7 +37144,7 @@
         <v>45937</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37220,7 +37222,7 @@
         <v>46147</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37293,7 +37295,7 @@
         <v>45358</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37371,7 +37373,7 @@
         <v>44631</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37449,7 +37451,7 @@
         <v>45138</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37522,7 +37524,7 @@
         <v>45691</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37595,7 +37597,7 @@
         <v>44943</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37668,7 +37670,7 @@
         <v>44796</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37746,7 +37748,7 @@
         <v>44586</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37819,7 +37821,7 @@
         <v>45947</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37897,7 +37899,7 @@
         <v>45384</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37970,7 +37972,7 @@
         <v>45093</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -38043,7 +38045,7 @@
         <v>44973</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -38116,7 +38118,7 @@
         <v>45950</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38189,7 +38191,7 @@
         <v>45949</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38262,7 +38264,7 @@
         <v>45949</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38340,7 +38342,7 @@
         <v>45948</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38413,7 +38415,7 @@
         <v>45949</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38491,7 +38493,7 @@
         <v>45904</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38564,7 +38566,7 @@
         <v>45394</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38637,7 +38639,7 @@
         <v>45054</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38710,7 +38712,7 @@
         <v>45007</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38783,7 +38785,7 @@
         <v>46153</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38856,7 +38858,7 @@
         <v>45568</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38929,7 +38931,7 @@
         <v>45960</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -39007,7 +39009,7 @@
         <v>45960</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -39085,7 +39087,7 @@
         <v>44993</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -39163,7 +39165,7 @@
         <v>46155</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39241,7 +39243,7 @@
         <v>44732</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39314,7 +39316,7 @@
         <v>45966</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39387,7 +39389,7 @@
         <v>45966</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39460,7 +39462,7 @@
         <v>46155</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39533,7 +39535,7 @@
         <v>44655</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39606,7 +39608,7 @@
         <v>45197</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39679,7 +39681,7 @@
         <v>46155</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39757,7 +39759,7 @@
         <v>45194</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39835,7 +39837,7 @@
         <v>44660</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39913,7 +39915,7 @@
         <v>45978</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39986,7 +39988,7 @@
         <v>45978</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -40064,7 +40066,7 @@
         <v>45978</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -40142,7 +40144,7 @@
         <v>45978</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40215,7 +40217,7 @@
         <v>46154</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40293,7 +40295,7 @@
         <v>46155</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40371,7 +40373,7 @@
         <v>45985</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40444,7 +40446,7 @@
         <v>46156</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40522,7 +40524,7 @@
         <v>45123</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40600,7 +40602,7 @@
         <v>44726</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40673,7 +40675,7 @@
         <v>44598</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40751,7 +40753,7 @@
         <v>45282</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40829,7 +40831,7 @@
         <v>46163</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40902,7 +40904,7 @@
         <v>46163</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40975,7 +40977,7 @@
         <v>45834</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -41048,7 +41050,7 @@
         <v>45076</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -41121,7 +41123,7 @@
         <v>45096</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41199,7 +41201,7 @@
         <v>45107</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41277,7 +41279,7 @@
         <v>46163</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41355,7 +41357,7 @@
         <v>45259</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41428,7 +41430,7 @@
         <v>45621</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41506,7 +41508,7 @@
         <v>44775</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41579,7 +41581,7 @@
         <v>45979</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41652,7 +41654,7 @@
         <v>46163</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41725,7 +41727,7 @@
         <v>45996</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41798,7 +41800,7 @@
         <v>46164</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41876,7 +41878,7 @@
         <v>45999</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41949,7 +41951,7 @@
         <v>44523</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -42022,7 +42024,7 @@
         <v>44981</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -42100,7 +42102,7 @@
         <v>46003</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -42173,7 +42175,7 @@
         <v>44803</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42251,7 +42253,7 @@
         <v>44676</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42324,7 +42326,7 @@
         <v>44596</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42397,7 +42399,7 @@
         <v>46008</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42470,7 +42472,7 @@
         <v>45082</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42543,7 +42545,7 @@
         <v>44972</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42621,7 +42623,7 @@
         <v>45047</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42699,7 +42701,7 @@
         <v>44952</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42772,7 +42774,7 @@
         <v>44775</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42845,7 +42847,7 @@
         <v>45154</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42918,7 +42920,7 @@
         <v>44938</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42991,7 +42993,7 @@
         <v>45114</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -43069,7 +43071,7 @@
         <v>45090</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -43147,7 +43149,7 @@
         <v>44525</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43220,7 +43222,7 @@
         <v>45842</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43293,7 +43295,7 @@
         <v>44512</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43366,7 +43368,7 @@
         <v>46040</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43439,7 +43441,7 @@
         <v>44890</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43517,7 +43519,7 @@
         <v>44895</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43595,7 +43597,7 @@
         <v>44908</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43668,7 +43670,7 @@
         <v>46043</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43741,7 +43743,7 @@
         <v>46043</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43814,7 +43816,7 @@
         <v>45751</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43887,7 +43889,7 @@
         <v>45762</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43960,7 +43962,7 @@
         <v>44973</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44033,7 +44035,7 @@
         <v>44466</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -44106,7 +44108,7 @@
         <v>46043</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -44179,7 +44181,7 @@
         <v>45702</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44257,7 +44259,7 @@
         <v>44553</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44335,7 +44337,7 @@
         <v>45680</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44413,7 +44415,7 @@
         <v>46176</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44486,7 +44488,7 @@
         <v>46176</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44559,7 +44561,7 @@
         <v>44874</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44637,7 +44639,7 @@
         <v>46176</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44710,7 +44712,7 @@
         <v>46048</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44788,7 +44790,7 @@
         <v>46050</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44866,7 +44868,7 @@
         <v>44515</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44944,7 +44946,7 @@
         <v>46176</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45017,7 +45019,7 @@
         <v>45170</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -45090,7 +45092,7 @@
         <v>46176</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -45163,7 +45165,7 @@
         <v>46176</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45236,7 +45238,7 @@
         <v>46176</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45309,7 +45311,7 @@
         <v>45740</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45382,7 +45384,7 @@
         <v>45012</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45460,7 +45462,7 @@
         <v>46178</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45538,7 +45540,7 @@
         <v>46056</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45616,7 +45618,7 @@
         <v>45202</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45689,7 +45691,7 @@
         <v>46056</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45767,7 +45769,7 @@
         <v>46056</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45845,7 +45847,7 @@
         <v>46056</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45923,7 +45925,7 @@
         <v>44586</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46001,7 +46003,7 @@
         <v>46058</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46079,7 +46081,7 @@
         <v>46058</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -46157,7 +46159,7 @@
         <v>46065</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46235,7 +46237,7 @@
         <v>46064</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -46308,7 +46310,7 @@
         <v>45462</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46386,7 +46388,7 @@
         <v>46064</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46459,7 +46461,7 @@
         <v>46065</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46537,7 +46539,7 @@
         <v>45005</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46610,7 +46612,7 @@
         <v>44715</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46683,7 +46685,7 @@
         <v>45195</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46756,7 +46758,7 @@
         <v>46181</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46834,7 +46836,7 @@
         <v>46181</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46912,7 +46914,7 @@
         <v>46181</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46990,7 +46992,7 @@
         <v>46181</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -47068,7 +47070,7 @@
         <v>44609</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -47141,7 +47143,7 @@
         <v>46182</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -47214,7 +47216,7 @@
         <v>46072</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -47292,7 +47294,7 @@
         <v>44523</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -47365,7 +47367,7 @@
         <v>44660</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47443,7 +47445,7 @@
         <v>44684</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47516,7 +47518,7 @@
         <v>46183</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47589,7 +47591,7 @@
         <v>46183</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47662,7 +47664,7 @@
         <v>44602</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47740,7 +47742,7 @@
         <v>44916</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47813,7 +47815,7 @@
         <v>46184</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47886,7 +47888,7 @@
         <v>44978</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47964,7 +47966,7 @@
         <v>44739</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -48042,7 +48044,7 @@
         <v>45040</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -48115,7 +48117,7 @@
         <v>45203</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -48193,7 +48195,7 @@
         <v>45233</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -48271,7 +48273,7 @@
         <v>46087</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -48349,7 +48351,7 @@
         <v>46087</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -48427,7 +48429,7 @@
         <v>45225</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48500,7 +48502,7 @@
         <v>46087</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48578,7 +48580,7 @@
         <v>44805</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48651,7 +48653,7 @@
         <v>44501</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48729,7 +48731,7 @@
         <v>46094</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48807,7 +48809,7 @@
         <v>46098</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48880,7 +48882,7 @@
         <v>46057</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48953,7 +48955,7 @@
         <v>45617</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -49026,7 +49028,7 @@
         <v>45476</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -49104,7 +49106,7 @@
         <v>46196</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -49182,7 +49184,7 @@
         <v>46195</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -49260,7 +49262,7 @@
         <v>46104</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -49333,7 +49335,7 @@
         <v>46106</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -49406,7 +49408,7 @@
         <v>46106</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -49479,7 +49481,7 @@
         <v>46106</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49552,7 +49554,7 @@
         <v>45560</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49625,7 +49627,7 @@
         <v>44665</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49703,7 +49705,7 @@
         <v>45142</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49781,7 +49783,7 @@
         <v>46108</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49854,7 +49856,7 @@
         <v>46107</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49932,7 +49934,7 @@
         <v>46107</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -50010,7 +50012,7 @@
         <v>45076</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -50088,7 +50090,7 @@
         <v>46108</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -50161,7 +50163,7 @@
         <v>46112</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -50234,7 +50236,7 @@
         <v>46112</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -50307,7 +50309,7 @@
         <v>46111</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -50380,7 +50382,7 @@
         <v>46112</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -50453,7 +50455,7 @@
         <v>46245</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50531,7 +50533,7 @@
         <v>46112</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50604,7 +50606,7 @@
         <v>46199</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50677,7 +50679,7 @@
         <v>46199</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50755,7 +50757,7 @@
         <v>46113</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50828,7 +50830,7 @@
         <v>46113</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50901,7 +50903,7 @@
         <v>46200</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50979,7 +50981,7 @@
         <v>45072</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -51052,7 +51054,7 @@
         <v>44591</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -51130,7 +51132,7 @@
         <v>45455</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -51208,7 +51210,7 @@
         <v>45089</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -51281,7 +51283,7 @@
         <v>46122</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -51359,7 +51361,7 @@
         <v>46200</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -51437,7 +51439,7 @@
         <v>45931</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51510,7 +51512,7 @@
         <v>44909</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51583,7 +51585,7 @@
         <v>46245</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51661,7 +51663,7 @@
         <v>46199</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51739,7 +51741,7 @@
         <v>46200</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51817,7 +51819,7 @@
         <v>44824</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51895,7 +51897,7 @@
         <v>46132</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51973,7 +51975,7 @@
         <v>44890</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -52051,7 +52053,7 @@
         <v>46246</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -52129,7 +52131,7 @@
         <v>44923</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -52207,7 +52209,7 @@
         <v>46134</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -52285,7 +52287,7 @@
         <v>46134</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -52363,7 +52365,7 @@
         <v>44977</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -52441,7 +52443,7 @@
         <v>45796</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -52514,7 +52516,7 @@
         <v>44795</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52592,7 +52594,7 @@
         <v>45819</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52670,7 +52672,7 @@
         <v>45778</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52743,7 +52745,7 @@
         <v>45621</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52821,7 +52823,7 @@
         <v>45621</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52899,7 +52901,7 @@
         <v>45621</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52977,7 +52979,7 @@
         <v>45835</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53055,7 +53057,7 @@
         <v>45812</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -53128,7 +53130,7 @@
         <v>46136</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -53206,7 +53208,7 @@
         <v>46246</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -53284,7 +53286,7 @@
         <v>44949</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -53357,7 +53359,7 @@
         <v>45176</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -53430,7 +53432,7 @@
         <v>45740</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -53503,7 +53505,7 @@
         <v>44998</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53576,7 +53578,7 @@
         <v>46178</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53654,7 +53656,7 @@
         <v>46206</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53727,7 +53729,7 @@
         <v>44522</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53800,7 +53802,7 @@
         <v>46206</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53873,7 +53875,7 @@
         <v>46206</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53946,7 +53948,7 @@
         <v>44536</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54019,7 +54021,7 @@
         <v>46252</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -54097,7 +54099,7 @@
         <v>46209</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -54170,7 +54172,7 @@
         <v>44578</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -54243,7 +54245,7 @@
         <v>46209</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -54321,7 +54323,7 @@
         <v>45213</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -54394,7 +54396,7 @@
         <v>44810</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -54467,7 +54469,7 @@
         <v>46209</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54545,7 +54547,7 @@
         <v>46209</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54623,7 +54625,7 @@
         <v>46209</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54701,7 +54703,7 @@
         <v>46209</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54779,7 +54781,7 @@
         <v>45259</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54852,7 +54854,7 @@
         <v>46211</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54925,7 +54927,7 @@
         <v>46211</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55003,7 +55005,7 @@
         <v>44841</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55076,7 +55078,7 @@
         <v>46211</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -55154,7 +55156,7 @@
         <v>44550</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -55227,7 +55229,7 @@
         <v>45337</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -55300,7 +55302,7 @@
         <v>46258</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -55378,7 +55380,7 @@
         <v>46258</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -55456,7 +55458,7 @@
         <v>46259</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -55534,7 +55536,7 @@
         <v>44923</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55612,7 +55614,7 @@
         <v>46258</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55690,7 +55692,7 @@
         <v>45225</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55763,7 +55765,7 @@
         <v>44953</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55836,7 +55838,7 @@
         <v>46258</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55914,7 +55916,7 @@
         <v>44552</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55987,7 +55989,7 @@
         <v>45467</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56065,7 +56067,7 @@
         <v>45147</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -56138,7 +56140,7 @@
         <v>44783</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -56216,7 +56218,7 @@
         <v>44973</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -56294,7 +56296,7 @@
         <v>46217</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -56372,7 +56374,7 @@
         <v>46217</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -56450,7 +56452,7 @@
         <v>46260</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -56528,7 +56530,7 @@
         <v>46219</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56601,7 +56603,7 @@
         <v>46262</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56679,7 +56681,7 @@
         <v>44972</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56757,7 +56759,7 @@
         <v>46219</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56830,7 +56832,7 @@
         <v>46219</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56903,7 +56905,7 @@
         <v>46181</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56976,7 +56978,7 @@
         <v>46219</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57054,7 +57056,7 @@
         <v>45687</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -57127,7 +57129,7 @@
         <v>46266</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -57205,7 +57207,7 @@
         <v>46266</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -57278,7 +57280,7 @@
         <v>46267</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -57356,7 +57358,7 @@
         <v>44725</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -57429,7 +57431,7 @@
         <v>45040</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -57502,7 +57504,7 @@
         <v>44915</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57575,7 +57577,7 @@
         <v>45097</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57648,7 +57650,7 @@
         <v>44531</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57726,7 +57728,7 @@
         <v>45468</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57799,7 +57801,7 @@
         <v>44496</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57872,7 +57874,7 @@
         <v>44938</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57945,7 +57947,7 @@
         <v>46253</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58018,7 +58020,7 @@
         <v>45597</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58091,7 +58093,7 @@
         <v>46063</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -58164,7 +58166,7 @@
         <v>45562</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -58242,7 +58244,7 @@
         <v>46274</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -58320,7 +58322,7 @@
         <v>46274</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -58398,7 +58400,7 @@
         <v>46274</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -58476,7 +58478,7 @@
         <v>46274</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -58554,7 +58556,7 @@
         <v>46279</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58632,7 +58634,7 @@
         <v>46279</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58710,7 +58712,7 @@
         <v>46276</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58788,7 +58790,7 @@
         <v>45538</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58866,7 +58868,7 @@
         <v>45520</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58944,7 +58946,7 @@
         <v>45569</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59017,7 +59019,7 @@
         <v>46276</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59095,7 +59097,7 @@
         <v>45013</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59168,7 +59170,7 @@
         <v>45546</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -59246,7 +59248,7 @@
         <v>45569</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -59319,7 +59321,7 @@
         <v>45574</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -59392,7 +59394,7 @@
         <v>45572</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -59465,7 +59467,7 @@
         <v>44598</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -59543,7 +59545,7 @@
         <v>45569</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59616,7 +59618,7 @@
         <v>46281</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59694,7 +59696,7 @@
         <v>46281</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59772,7 +59774,7 @@
         <v>45572</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59845,7 +59847,7 @@
         <v>45253</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59918,7 +59920,7 @@
         <v>45670</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59991,7 +59993,7 @@
         <v>45499</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60069,7 +60071,7 @@
         <v>45456</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60147,7 +60149,7 @@
         <v>46239</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -60225,7 +60227,7 @@
         <v>45797</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -60298,7 +60300,7 @@
         <v>46239</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -60376,7 +60378,7 @@
         <v>46240</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -60449,7 +60451,7 @@
         <v>46282</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -60527,7 +60529,7 @@
         <v>46282</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -60605,7 +60607,7 @@
         <v>46241</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60683,7 +60685,7 @@
         <v>46240</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60761,7 +60763,7 @@
         <v>46240</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60839,7 +60841,7 @@
         <v>46240</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60917,7 +60919,7 @@
         <v>45734</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60990,7 +60992,7 @@
         <v>45524</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61063,7 +61065,7 @@
         <v>45749</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61141,7 +61143,7 @@
         <v>45740</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61214,7 +61216,7 @@
         <v>45632</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -61287,7 +61289,7 @@
         <v>45805</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -61360,7 +61362,7 @@
         <v>45811</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -61433,7 +61435,7 @@
         <v>45812</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -61506,7 +61508,7 @@
         <v>45817</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -61584,7 +61586,7 @@
         <v>45708</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61662,7 +61664,7 @@
         <v>45813</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61740,7 +61742,7 @@
         <v>45813</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61818,7 +61820,7 @@
         <v>45824</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61891,7 +61893,7 @@
         <v>45813</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61969,7 +61971,7 @@
         <v>45813</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62047,7 +62049,7 @@
         <v>45831</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62120,7 +62122,7 @@
         <v>45830</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62193,7 +62195,7 @@
         <v>45830</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62266,7 +62268,7 @@
         <v>45833</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -62339,7 +62341,7 @@
         <v>45813</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -62417,7 +62419,7 @@
         <v>45841</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -62495,7 +62497,7 @@
         <v>45807</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -62568,7 +62570,7 @@
         <v>45842</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62641,7 +62643,7 @@
         <v>45467</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62714,7 +62716,7 @@
         <v>45719</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62787,7 +62789,7 @@
         <v>45770</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62865,7 +62867,7 @@
         <v>45759</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62938,7 +62940,7 @@
         <v>45869</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -63011,7 +63013,7 @@
         <v>44970</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -63084,7 +63086,7 @@
         <v>44964</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -63157,7 +63159,7 @@
         <v>45078</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -63230,7 +63232,7 @@
         <v>45428</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -63303,7 +63305,7 @@
         <v>45428</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -63376,7 +63378,7 @@
         <v>44729</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -63454,7 +63456,7 @@
         <v>45390</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -63532,7 +63534,7 @@
         <v>44672</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -63605,7 +63607,7 @@
         <v>45182</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -63683,7 +63685,7 @@
         <v>45916</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63756,7 +63758,7 @@
         <v>45957</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63829,7 +63831,7 @@
         <v>46034</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63907,7 +63909,7 @@
         <v>46089</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>46204</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>45114</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45106</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>45590</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>46132</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45061</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45063</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>45660</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>43955</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>45659</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>46132</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46030</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45439</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>46183</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>45106</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>46279</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46205</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44918</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>45182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>46009</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>46196</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>45210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>46132</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44865</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>45681</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>44662</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44482</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>44938</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>45622</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45076</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45660</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>45190</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45947</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>46205</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>44771</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>44935</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>45796</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>45891</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>44644</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>45226</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>44194</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>45076</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44636</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>46170</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>46071</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>45840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>45362</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>44837</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>45198</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44474</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>44588</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45160</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>44779</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>44727</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>45205</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44739</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>45238</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44819</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>44511</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>44684</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45412</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>45078</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>45107</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>44728</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>46265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>44525</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>45315</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45545</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>44858</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>46048</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>45999</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45070</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45520</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>44984</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45699</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>45390</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>44874</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>45372</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>45460</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>46121</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>45999</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45446</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>44903</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>46161</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>44729</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>44683</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>45274</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>45895</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>46089</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44495</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44515</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44578</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>44778</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45063</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45425</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44883</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>45583</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45951</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>46001</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>46142</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45743</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44644</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>46252</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>45045</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>46287</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>45063</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>45775</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>45068</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45393</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44782</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>44859</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>44687</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44813</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>44622</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>44501</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>44715</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>44792</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>44991</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45154</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45329</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>44875</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>45896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45436</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>46056</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>45678</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>46062</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>46098</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>46063</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>44712</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45831</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>46139</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>44607</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44985</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45213</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>46154</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45156</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>44517</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44606</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>46195</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>46195</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>44572</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45387</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>46211</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>46211</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45162</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>46259</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>46002</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>46260</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45135</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>46268</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>46275</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>46235</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>44979</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>46290</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45007</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>44915</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>45013</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45695</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>45250</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>45078</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44998</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>45160</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45384</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44509</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45513</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44726</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44610</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45078</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45218</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>45178</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45007</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44491</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>45078</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45820</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>45728</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>46112</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>46191</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44614</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>44732</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44729</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>44622</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>44501</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44555</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44622</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>44687</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44664</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>44651</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>44644</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44868</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>44498</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>44491</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>44838</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>44691</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>44577</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44525</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44661</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44649</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>44622</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44613</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>44588</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>44725</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>44725</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>44852</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44519</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44598</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>44692</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44691</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>44694</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>44659</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>44865</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>44715</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44664</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44757</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44861</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>44873</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>44661</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44501</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>44809</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>44809</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>44813</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44810</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>44635</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>44712</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>44669</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44687</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44608</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>44728</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44872</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>44770</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44739</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44467</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44620</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>44687</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>44635</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44676</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44643</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>44669</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>44466</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>44814</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>45047</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45044</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44860</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45102</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45419</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45384</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>44928</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>44928</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>45462</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>45433</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>44890</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45394</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>45467</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44963</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45519</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>45257</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44959</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45138</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>44466</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>44894</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>44973</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45147</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>44890</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45456</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>45670</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>45499</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>45482</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45797</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>44512</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44978</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45337</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>44916</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>45516</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>45516</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>44915</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>45895</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>45895</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>46040</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>45895</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>45895</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45895</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>44560</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>46043</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>44972</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>45898</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>46043</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>46043</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>46048</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45797</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>45797</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>46050</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45797</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>44874</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>45817</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>44586</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>45544</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45670</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>44665</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>45476</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>46056</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>46056</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>46056</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>44536</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>45749</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>45909</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46056</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44896</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>44896</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>46058</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>46058</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>45063</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45524</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>45740</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>46064</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>46064</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>44501</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>44555</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>46065</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>46065</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45734</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45740</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45924</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45632</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45097</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>46072</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>44923</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45805</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>44599</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>44938</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>45202</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45931</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>44915</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>46087</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>44533</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>46087</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>46087</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>44943</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>45937</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>45384</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>46094</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>46098</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>44775</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>45812</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         <v>46104</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>45950</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>44725</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45949</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>45947</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45949</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>45949</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>45948</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>46106</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>46107</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>45904</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>46107</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>46106</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>46106</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>46111</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>46108</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>46108</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>46113</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>46112</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>44732</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>46113</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>44923</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>46112</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35289,7 +35289,7 @@
         <v>46112</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45114</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>46112</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>45960</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>44783</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45960</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>46122</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45931</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>45966</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35971,7 +35971,7 @@
         <v>45966</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>44591</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44631</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>45811</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45708</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>44991</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45680</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>45012</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>45817</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>44496</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>45271</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45978</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>45978</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>45978</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>46132</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>45978</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45617</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>46134</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45455</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>46134</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>46136</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45840</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>45985</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45621</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45621</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>45621</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>46136</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45102</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45796</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>44512</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45187</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>45005</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>44803</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>44687</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38553,7 +38553,7 @@
         <v>45076</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>45996</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45819</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>45778</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45979</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>45805</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45999</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>45755</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45733</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>46034</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>46003</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>45813</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45975</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>44613</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45760</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>46008</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>45813</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45835</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
         <v>44495</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>45812</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>45110</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45813</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45813</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40282,7 +40282,7 @@
         <v>45824</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>46139</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>44991</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>46034</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45337</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>46139</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>46141</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         <v>46104</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>45250</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>44531</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>46104</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>46141</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>45212</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45830</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45830</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>44596</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>46147</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45233</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>46147</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45831</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>45833</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>46153</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45259</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>46154</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45646</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>46155</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>45089</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42298,7 +42298,7 @@
         <v>46155</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>46156</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>46155</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>46155</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>45090</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>45054</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42761,7 +42761,7 @@
         <v>45560</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42834,7 +42834,7 @@
         <v>44578</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45813</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>45040</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -43058,7 +43058,7 @@
         <v>45834</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -43131,7 +43131,7 @@
         <v>45841</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -43209,7 +43209,7 @@
         <v>45076</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45096</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45842</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>45807</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>46163</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>46163</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>46163</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>46164</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45379</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>46163</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>44953</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>45719</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>45467</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>45040</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -44251,7 +44251,7 @@
         <v>45770</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>44522</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44402,7 +44402,7 @@
         <v>45075</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>44909</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>45358</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45530</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44704,7 +44704,7 @@
         <v>45762</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44777,7 +44777,7 @@
         <v>45162</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45842</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>45751</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>45759</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45074,7 +45074,7 @@
         <v>44972</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>44560</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45123</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>45520</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45386,7 +45386,7 @@
         <v>46176</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>46176</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
         <v>44973</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>46176</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45678,7 +45678,7 @@
         <v>46176</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45751,7 +45751,7 @@
         <v>46176</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>45740</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45897,7 +45897,7 @@
         <v>46176</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>46176</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>45869</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>44977</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>46181</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46272,7 +46272,7 @@
         <v>46178</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>46181</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>46181</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>46181</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>44553</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46662,7 +46662,7 @@
         <v>46182</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46735,7 +46735,7 @@
         <v>46183</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>44552</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>46183</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45114</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>45079</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45148</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>46184</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -47256,7 +47256,7 @@
         <v>44952</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45146</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45468</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45572</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>44591</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
         <v>46057</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>46195</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45191</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47860,7 +47860,7 @@
         <v>45341</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47933,7 +47933,7 @@
         <v>46196</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>44598</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45107</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>44602</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -48245,7 +48245,7 @@
         <v>46200</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -48323,7 +48323,7 @@
         <v>46200</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>46200</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>44643</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>46199</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48630,7 +48630,7 @@
         <v>46199</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>46199</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>44970</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45225</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45082</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -49000,7 +49000,7 @@
         <v>46209</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -49078,7 +49078,7 @@
         <v>46209</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>44795</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -49234,7 +49234,7 @@
         <v>46252</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>45197</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>46206</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>46206</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>46178</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49609,7 +49609,7 @@
         <v>45621</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>44805</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49760,7 +49760,7 @@
         <v>45230</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>45230</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49906,7 +49906,7 @@
         <v>46209</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>46209</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>46209</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>46206</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>44706</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -50281,7 +50281,7 @@
         <v>44651</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>46209</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>44609</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
         <v>45687</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>45239</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>46211</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50734,7 +50734,7 @@
         <v>46211</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>44643</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45195</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>46211</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>46258</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>46258</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>46258</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -51270,7 +51270,7 @@
         <v>44684</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>46258</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -51421,7 +51421,7 @@
         <v>45093</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -51494,7 +51494,7 @@
         <v>44676</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51567,7 +51567,7 @@
         <v>45455</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51645,7 +51645,7 @@
         <v>45358</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>46259</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51801,7 +51801,7 @@
         <v>44895</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>46217</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51957,7 +51957,7 @@
         <v>45202</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>46260</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -52108,7 +52108,7 @@
         <v>46217</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>44664</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>46262</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>44746</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>44660</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>46219</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>46219</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>46219</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52712,7 +52712,7 @@
         <v>46181</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52785,7 +52785,7 @@
         <v>44651</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         <v>46219</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52936,7 +52936,7 @@
         <v>44810</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45176</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53082,7 +53082,7 @@
         <v>44783</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -53160,7 +53160,7 @@
         <v>45174</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45212</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -53316,7 +53316,7 @@
         <v>45757</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -53394,7 +53394,7 @@
         <v>45194</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45233</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -53550,7 +53550,7 @@
         <v>45702</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53628,7 +53628,7 @@
         <v>46266</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>46266</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53779,7 +53779,7 @@
         <v>44770</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>44841</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53930,7 +53930,7 @@
         <v>44755</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>46267</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45225</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>45362</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -54227,7 +54227,7 @@
         <v>44775</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45203</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -54378,7 +54378,7 @@
         <v>45007</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>44796</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -54529,7 +54529,7 @@
         <v>44476</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54607,7 +54607,7 @@
         <v>46274</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>46253</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54758,7 +54758,7 @@
         <v>46063</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54831,7 +54831,7 @@
         <v>46274</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54909,7 +54909,7 @@
         <v>46274</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54987,7 +54987,7 @@
         <v>46274</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55065,7 +55065,7 @@
         <v>45054</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
         <v>45337</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>46276</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -55289,7 +55289,7 @@
         <v>45259</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -55362,7 +55362,7 @@
         <v>44496</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>46276</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>46279</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>46279</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55669,7 +55669,7 @@
         <v>45208</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>46239</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55820,7 +55820,7 @@
         <v>45520</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>46281</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>46281</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>46282</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56132,7 +56132,7 @@
         <v>46282</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -56210,7 +56210,7 @@
         <v>46239</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         <v>46240</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>45496</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -56439,7 +56439,7 @@
         <v>46286</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -56512,7 +56512,7 @@
         <v>46240</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -56590,7 +56590,7 @@
         <v>46240</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56668,7 +56668,7 @@
         <v>46240</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56746,7 +56746,7 @@
         <v>45520</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56824,7 +56824,7 @@
         <v>46241</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56902,7 +56902,7 @@
         <v>44586</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>44973</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -57053,7 +57053,7 @@
         <v>44993</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57131,7 +57131,7 @@
         <v>45040</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>46287</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>44874</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>46245</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -57428,7 +57428,7 @@
         <v>44572</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -57501,7 +57501,7 @@
         <v>46245</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -57579,7 +57579,7 @@
         <v>44949</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57652,7 +57652,7 @@
         <v>44953</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57725,7 +57725,7 @@
         <v>45112</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57803,7 +57803,7 @@
         <v>44739</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>46246</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57959,7 +57959,7 @@
         <v>44613</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -58032,7 +58032,7 @@
         <v>46289</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58105,7 +58105,7 @@
         <v>46246</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58183,7 +58183,7 @@
         <v>45462</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -58261,7 +58261,7 @@
         <v>46289</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -58334,7 +58334,7 @@
         <v>44905</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45090</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -58485,7 +58485,7 @@
         <v>45244</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>44523</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -58631,7 +58631,7 @@
         <v>45107</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58709,7 +58709,7 @@
         <v>44511</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58782,7 +58782,7 @@
         <v>46290</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58855,7 +58855,7 @@
         <v>45282</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58933,7 +58933,7 @@
         <v>44515</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -59011,7 +59011,7 @@
         <v>44576</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>44655</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59162,7 +59162,7 @@
         <v>44998</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59235,7 +59235,7 @@
         <v>45561</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -59313,7 +59313,7 @@
         <v>44660</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -59391,7 +59391,7 @@
         <v>44963</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -59464,7 +59464,7 @@
         <v>45691</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -59537,7 +59537,7 @@
         <v>44515</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -59615,7 +59615,7 @@
         <v>45154</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59688,7 +59688,7 @@
         <v>44599</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59761,7 +59761,7 @@
         <v>44950</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59839,7 +59839,7 @@
         <v>45194</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59917,7 +59917,7 @@
         <v>45568</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59990,7 +59990,7 @@
         <v>44908</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>44591</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60136,7 +60136,7 @@
         <v>45152</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60209,7 +60209,7 @@
         <v>45102</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -60287,7 +60287,7 @@
         <v>44523</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -60360,7 +60360,7 @@
         <v>44725</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -60433,7 +60433,7 @@
         <v>44726</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -60506,7 +60506,7 @@
         <v>45213</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45142</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -60657,7 +60657,7 @@
         <v>45218</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60730,7 +60730,7 @@
         <v>44775</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60803,7 +60803,7 @@
         <v>45102</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60881,7 +60881,7 @@
         <v>45170</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60954,7 +60954,7 @@
         <v>44987</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -61027,7 +61027,7 @@
         <v>44768</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61105,7 +61105,7 @@
         <v>45072</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61178,7 +61178,7 @@
         <v>44991</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>44824</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -61329,7 +61329,7 @@
         <v>45063</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -61407,7 +61407,7 @@
         <v>44715</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -61480,7 +61480,7 @@
         <v>44482</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -61553,7 +61553,7 @@
         <v>44550</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -61626,7 +61626,7 @@
         <v>44970</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61699,7 +61699,7 @@
         <v>44809</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61772,7 +61772,7 @@
         <v>44981</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61850,7 +61850,7 @@
         <v>45621</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61928,7 +61928,7 @@
         <v>45093</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -62006,7 +62006,7 @@
         <v>44525</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62079,7 +62079,7 @@
         <v>45621</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62157,7 +62157,7 @@
         <v>45225</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>45597</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62303,7 +62303,7 @@
         <v>44938</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -62376,7 +62376,7 @@
         <v>45562</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -62454,7 +62454,7 @@
         <v>45574</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -62527,7 +62527,7 @@
         <v>45538</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45253</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62678,7 +62678,7 @@
         <v>45569</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62751,7 +62751,7 @@
         <v>45546</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62829,7 +62829,7 @@
         <v>45572</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>44598</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62980,7 +62980,7 @@
         <v>45569</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -63053,7 +63053,7 @@
         <v>45569</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -63126,7 +63126,7 @@
         <v>45013</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -63199,7 +63199,7 @@
         <v>45520</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -63277,7 +63277,7 @@
         <v>45572</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -63350,7 +63350,7 @@
         <v>44729</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -63428,7 +63428,7 @@
         <v>44672</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -63501,7 +63501,7 @@
         <v>44964</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -63574,7 +63574,7 @@
         <v>45078</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -63647,7 +63647,7 @@
         <v>45428</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -63720,7 +63720,7 @@
         <v>45428</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63793,7 +63793,7 @@
         <v>45390</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63871,7 +63871,7 @@
         <v>45182</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45916</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -64022,7 +64022,7 @@
         <v>45957</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -64095,7 +64095,7 @@
         <v>46034</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -64173,7 +64173,7 @@
         <v>46089</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>46204</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>45114</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45106</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>45590</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>46132</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45061</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45063</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>45660</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>43955</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>45659</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>46132</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46030</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45439</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>46183</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>45106</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>46279</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46205</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44918</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>45182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>46009</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>46196</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>45210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>46132</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44865</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>45681</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>44662</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44482</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>44938</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>45622</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45076</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45660</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>45190</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45947</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>46205</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>44771</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>44935</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>45796</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>45891</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>44644</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>45226</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>44194</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>45076</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44636</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>46170</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>46071</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>45840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>45362</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>44837</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>45198</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44474</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>44588</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45160</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>44779</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>44727</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>45205</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44739</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>45238</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44819</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>44511</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>44684</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45412</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>45078</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>45107</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>44728</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>46265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>44525</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>45315</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45545</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>44858</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>46048</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>45999</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45070</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45520</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>44984</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45699</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>45390</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>44874</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>45372</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>45460</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>46121</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>45999</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45446</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>44903</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>46161</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>44729</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>44683</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>45274</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>45895</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>46089</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44495</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44515</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44578</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>44778</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45063</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45425</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44883</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>45583</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45951</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>46001</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>46142</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45743</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44644</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>46252</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>45045</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>46287</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>45063</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>45775</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>45068</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45393</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44782</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>44859</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>44687</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44813</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>44622</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>44501</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>44715</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>44792</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>44991</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45154</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45329</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>44875</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>45896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45436</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>46056</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>45678</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>46062</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>46098</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>46063</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>44712</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45831</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>46139</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>44607</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44985</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45213</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>46154</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45156</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>44517</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44606</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>46195</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>46195</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>44572</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45387</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>46211</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>46211</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45162</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>46259</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>46002</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>46260</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45135</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>46268</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>46275</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>46235</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>44979</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>46290</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45007</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>44915</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>45013</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45695</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>45250</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>45078</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44998</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>45160</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45384</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44509</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45513</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44726</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44610</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45078</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45218</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>45178</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45007</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44491</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>45078</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45820</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>45728</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>46112</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>46191</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44614</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>44732</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44729</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>44622</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>44501</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44555</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44622</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>44687</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44664</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>44651</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>44644</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44868</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>44498</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>44491</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>44838</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>44691</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>44577</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44525</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44661</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44649</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>44622</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44613</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>44588</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>44725</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>44725</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>44852</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44519</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44598</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>44692</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44691</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>44694</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>44659</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>44865</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>44715</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44664</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44757</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44861</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>44873</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>44661</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44501</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>44809</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>44809</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>44813</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44810</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>44635</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>44712</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>44669</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44687</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44608</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>44728</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44872</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>44770</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44739</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44467</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44620</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>44687</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>44635</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44676</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44643</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>44669</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>44466</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>44814</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>45047</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45044</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44860</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45102</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45419</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45384</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>44928</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>44928</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>45462</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>45433</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>44890</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45394</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>45467</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44963</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45519</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>45257</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44959</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45138</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>44466</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>44894</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>44973</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45147</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>44890</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45456</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>45670</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>45499</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>45482</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45797</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>44512</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44978</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45337</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>44916</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>45516</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>45516</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>44915</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>45895</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>45895</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>46040</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>45895</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>45895</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45895</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>44560</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>46043</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>44972</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>45898</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>46043</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>46043</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>46048</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45797</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>45797</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>46050</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45797</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>44874</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>45817</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>44586</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>45544</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45670</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>44665</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>45476</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>46056</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>46056</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>46056</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>44536</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>45749</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>45909</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46056</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44896</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>44896</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>46058</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>46058</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>45063</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45524</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>45740</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>46064</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>46064</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>44501</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>44555</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>46065</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>46065</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45734</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45740</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45924</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45632</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45097</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>46072</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>44923</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45805</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>44599</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>44938</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>45202</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45931</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>44915</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>46087</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>44533</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>46087</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>46087</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>44943</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>45937</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>45384</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>46094</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>46098</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>44775</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>45812</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         <v>46104</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>45950</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>44725</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45949</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>45947</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45949</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>45949</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>45948</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>46106</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>46107</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>45904</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>46107</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>46106</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>46106</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>46111</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>46108</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>46108</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>46113</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>46112</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>44732</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>46113</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>44923</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>46112</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35289,7 +35289,7 @@
         <v>46112</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45114</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>46112</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>45960</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>44783</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45960</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>46122</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45931</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>45966</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35971,7 +35971,7 @@
         <v>45966</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>44591</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44631</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>45811</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45708</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>44991</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45680</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>45012</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>45817</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>44496</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>45271</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45978</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>45978</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>45978</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>46132</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>45978</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45617</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>46134</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45455</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>46134</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>46136</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45840</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>45985</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45621</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45621</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>45621</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>46136</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45102</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45796</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>44512</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45187</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>45005</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>44803</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>44687</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38553,7 +38553,7 @@
         <v>45076</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>45996</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45819</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>45778</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45979</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>45805</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45999</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>45755</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45733</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>46034</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>46003</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>45813</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45975</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>44613</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45760</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>46008</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>45813</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45835</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
         <v>44495</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>45812</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>45110</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45813</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45813</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40282,7 +40282,7 @@
         <v>45824</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>46139</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>44991</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>46034</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45337</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>46139</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>46141</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         <v>46104</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>45250</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>44531</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>46104</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>46141</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>45212</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45830</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45830</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>44596</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>46147</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45233</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>46147</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45831</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>45833</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>46153</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45259</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>46154</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45646</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>46155</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>45089</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42298,7 +42298,7 @@
         <v>46155</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>46156</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>46155</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>46155</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>45090</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>45054</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42761,7 +42761,7 @@
         <v>45560</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42834,7 +42834,7 @@
         <v>44578</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45813</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>45040</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -43058,7 +43058,7 @@
         <v>45834</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -43131,7 +43131,7 @@
         <v>45841</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -43209,7 +43209,7 @@
         <v>45076</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45096</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45842</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>45807</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>46163</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>46163</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>46163</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>46164</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45379</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>46163</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>44953</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>45719</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>45467</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>45040</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -44251,7 +44251,7 @@
         <v>45770</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>44522</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44402,7 +44402,7 @@
         <v>45075</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>44909</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>45358</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45530</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44704,7 +44704,7 @@
         <v>45762</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44777,7 +44777,7 @@
         <v>45162</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45842</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>45751</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>45759</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45074,7 +45074,7 @@
         <v>44972</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>44560</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45123</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>45520</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45386,7 +45386,7 @@
         <v>46176</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>46176</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
         <v>44973</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>46176</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45678,7 +45678,7 @@
         <v>46176</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45751,7 +45751,7 @@
         <v>46176</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>45740</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45897,7 +45897,7 @@
         <v>46176</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>46176</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>45869</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>44977</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>46181</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46272,7 +46272,7 @@
         <v>46178</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>46181</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>46181</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>46181</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>44553</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46662,7 +46662,7 @@
         <v>46182</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46735,7 +46735,7 @@
         <v>46183</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>44552</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>46183</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>45114</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>45079</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45148</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>46184</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -47256,7 +47256,7 @@
         <v>44952</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45146</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45468</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45572</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>44591</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
         <v>46057</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>46195</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45191</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47860,7 +47860,7 @@
         <v>45341</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47933,7 +47933,7 @@
         <v>46196</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>44598</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45107</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>44602</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -48245,7 +48245,7 @@
         <v>46200</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -48323,7 +48323,7 @@
         <v>46200</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>46200</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>44643</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>46199</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48630,7 +48630,7 @@
         <v>46199</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>46199</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>44970</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45225</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45082</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -49000,7 +49000,7 @@
         <v>46209</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -49078,7 +49078,7 @@
         <v>46209</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>44795</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -49234,7 +49234,7 @@
         <v>46252</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>45197</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>46206</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>46206</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>46178</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49609,7 +49609,7 @@
         <v>45621</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>44805</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49760,7 +49760,7 @@
         <v>45230</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>45230</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49906,7 +49906,7 @@
         <v>46209</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>46209</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>46209</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>46206</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>44706</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -50281,7 +50281,7 @@
         <v>44651</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>46209</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>44609</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
         <v>45687</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>45239</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>46211</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50734,7 +50734,7 @@
         <v>46211</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>44643</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45195</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>46211</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>46258</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>46258</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>46258</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -51270,7 +51270,7 @@
         <v>44684</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>46258</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -51421,7 +51421,7 @@
         <v>45093</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -51494,7 +51494,7 @@
         <v>44676</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51567,7 +51567,7 @@
         <v>45455</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51645,7 +51645,7 @@
         <v>45358</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>46259</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51801,7 +51801,7 @@
         <v>44895</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>46217</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51957,7 +51957,7 @@
         <v>45202</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>46260</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -52108,7 +52108,7 @@
         <v>46217</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>44664</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>46262</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>44746</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>44660</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>46219</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>46219</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>46219</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52712,7 +52712,7 @@
         <v>46181</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52785,7 +52785,7 @@
         <v>44651</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         <v>46219</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52936,7 +52936,7 @@
         <v>44810</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45176</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53082,7 +53082,7 @@
         <v>44783</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -53160,7 +53160,7 @@
         <v>45174</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45212</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -53316,7 +53316,7 @@
         <v>45757</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -53394,7 +53394,7 @@
         <v>45194</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45233</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -53550,7 +53550,7 @@
         <v>45702</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53628,7 +53628,7 @@
         <v>46266</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>46266</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53779,7 +53779,7 @@
         <v>44770</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>44841</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53930,7 +53930,7 @@
         <v>44755</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>46267</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45225</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>45362</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -54227,7 +54227,7 @@
         <v>44775</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45203</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -54378,7 +54378,7 @@
         <v>45007</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>44796</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -54529,7 +54529,7 @@
         <v>44476</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54607,7 +54607,7 @@
         <v>46274</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>46253</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54758,7 +54758,7 @@
         <v>46063</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54831,7 +54831,7 @@
         <v>46274</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54909,7 +54909,7 @@
         <v>46274</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54987,7 +54987,7 @@
         <v>46274</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55065,7 +55065,7 @@
         <v>45054</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
         <v>45337</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>46276</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -55289,7 +55289,7 @@
         <v>45259</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -55362,7 +55362,7 @@
         <v>44496</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>46276</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>46279</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>46279</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55669,7 +55669,7 @@
         <v>45208</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>46239</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55820,7 +55820,7 @@
         <v>45520</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>46281</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>46281</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>46282</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56132,7 +56132,7 @@
         <v>46282</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -56210,7 +56210,7 @@
         <v>46239</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         <v>46240</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>45496</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -56439,7 +56439,7 @@
         <v>46286</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -56512,7 +56512,7 @@
         <v>46240</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -56590,7 +56590,7 @@
         <v>46240</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56668,7 +56668,7 @@
         <v>46240</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56746,7 +56746,7 @@
         <v>45520</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56824,7 +56824,7 @@
         <v>46241</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56902,7 +56902,7 @@
         <v>44586</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>44973</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -57053,7 +57053,7 @@
         <v>44993</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57131,7 +57131,7 @@
         <v>45040</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>46287</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>44874</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>46245</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -57428,7 +57428,7 @@
         <v>44572</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -57501,7 +57501,7 @@
         <v>46245</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -57579,7 +57579,7 @@
         <v>44949</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57652,7 +57652,7 @@
         <v>44953</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57725,7 +57725,7 @@
         <v>45112</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57803,7 +57803,7 @@
         <v>44739</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>46246</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57959,7 +57959,7 @@
         <v>44613</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -58032,7 +58032,7 @@
         <v>46289</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58105,7 +58105,7 @@
         <v>46246</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58183,7 +58183,7 @@
         <v>45462</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -58261,7 +58261,7 @@
         <v>46289</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -58334,7 +58334,7 @@
         <v>44905</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45090</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -58485,7 +58485,7 @@
         <v>45244</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>44523</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -58631,7 +58631,7 @@
         <v>45107</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58709,7 +58709,7 @@
         <v>44511</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58782,7 +58782,7 @@
         <v>46290</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58855,7 +58855,7 @@
         <v>45282</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58933,7 +58933,7 @@
         <v>44515</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -59011,7 +59011,7 @@
         <v>44576</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>44655</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59162,7 +59162,7 @@
         <v>44998</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59235,7 +59235,7 @@
         <v>45561</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -59313,7 +59313,7 @@
         <v>44660</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -59391,7 +59391,7 @@
         <v>44963</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -59464,7 +59464,7 @@
         <v>45691</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -59537,7 +59537,7 @@
         <v>44515</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -59615,7 +59615,7 @@
         <v>45154</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59688,7 +59688,7 @@
         <v>44599</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59761,7 +59761,7 @@
         <v>44950</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59839,7 +59839,7 @@
         <v>45194</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59917,7 +59917,7 @@
         <v>45568</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59990,7 +59990,7 @@
         <v>44908</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>44591</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60136,7 +60136,7 @@
         <v>45152</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60209,7 +60209,7 @@
         <v>45102</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -60287,7 +60287,7 @@
         <v>44523</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -60360,7 +60360,7 @@
         <v>44725</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -60433,7 +60433,7 @@
         <v>44726</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -60506,7 +60506,7 @@
         <v>45213</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45142</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -60657,7 +60657,7 @@
         <v>45218</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60730,7 +60730,7 @@
         <v>44775</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60803,7 +60803,7 @@
         <v>45102</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60881,7 +60881,7 @@
         <v>45170</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60954,7 +60954,7 @@
         <v>44987</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -61027,7 +61027,7 @@
         <v>44768</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61105,7 +61105,7 @@
         <v>45072</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61178,7 +61178,7 @@
         <v>44991</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>44824</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -61329,7 +61329,7 @@
         <v>45063</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -61407,7 +61407,7 @@
         <v>44715</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -61480,7 +61480,7 @@
         <v>44482</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -61553,7 +61553,7 @@
         <v>44550</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -61626,7 +61626,7 @@
         <v>44970</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61699,7 +61699,7 @@
         <v>44809</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61772,7 +61772,7 @@
         <v>44981</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61850,7 +61850,7 @@
         <v>45621</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61928,7 +61928,7 @@
         <v>45093</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -62006,7 +62006,7 @@
         <v>44525</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62079,7 +62079,7 @@
         <v>45621</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62157,7 +62157,7 @@
         <v>45225</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>45597</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62303,7 +62303,7 @@
         <v>44938</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -62376,7 +62376,7 @@
         <v>45562</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -62454,7 +62454,7 @@
         <v>45574</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -62527,7 +62527,7 @@
         <v>45538</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45253</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62678,7 +62678,7 @@
         <v>45569</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62751,7 +62751,7 @@
         <v>45546</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62829,7 +62829,7 @@
         <v>45572</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>44598</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62980,7 +62980,7 @@
         <v>45569</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -63053,7 +63053,7 @@
         <v>45569</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -63126,7 +63126,7 @@
         <v>45013</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -63199,7 +63199,7 @@
         <v>45520</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -63277,7 +63277,7 @@
         <v>45572</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -63350,7 +63350,7 @@
         <v>44729</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -63428,7 +63428,7 @@
         <v>44672</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -63501,7 +63501,7 @@
         <v>44964</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -63574,7 +63574,7 @@
         <v>45078</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -63647,7 +63647,7 @@
         <v>45428</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -63720,7 +63720,7 @@
         <v>45428</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63793,7 +63793,7 @@
         <v>45390</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63871,7 +63871,7 @@
         <v>45182</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45916</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -64022,7 +64022,7 @@
         <v>45957</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -64095,7 +64095,7 @@
         <v>46034</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -64173,7 +64173,7 @@
         <v>46089</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>46204</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>45114</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45106</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>46132</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45590</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>45061</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>45063</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45660</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>43955</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>46132</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>45439</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>46030</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>46183</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45106</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>46279</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>46205</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>44918</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>45182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>46009</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>46196</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>46132</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>45210</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>44865</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45681</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44662</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>44482</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45660</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45622</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>45076</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45947</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>44771</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>45190</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>46205</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44935</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>45796</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>45891</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44644</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>45226</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>44194</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45076</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>44636</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>46170</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>44474</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>46071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>45840</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>44837</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>45362</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>45520</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45198</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>45160</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>44588</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>44779</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>44739</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>45238</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>44727</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>45205</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>44819</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>44511</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44684</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>44874</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>45412</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>44728</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>45078</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>46265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44525</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>45107</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>45315</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>46048</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45070</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>44984</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>45999</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44858</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45545</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>45699</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>45390</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>44874</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>45460</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>46121</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45999</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>45372</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>44903</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>46161</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>44683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44729</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>45446</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>45274</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>45895</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>46089</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44495</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>44515</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>44578</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44778</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45068</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>45045</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45393</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>45425</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45951</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>45775</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45583</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>46001</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>44644</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>46142</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45743</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45063</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>44883</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45063</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>46287</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>46252</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>44782</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44859</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>44687</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44813</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44622</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>44501</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>44715</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         <v>44792</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>44509</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>44606</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>45154</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45896</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>46056</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>46062</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>45329</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>46098</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45678</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>46063</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>45695</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>44607</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>45831</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>44985</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>46139</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44712</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45384</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>45160</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>46154</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>45436</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44915</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>45013</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>46195</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>46195</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>44572</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44991</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>44875</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45162</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>46211</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>46211</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>46259</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>46002</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45135</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>46260</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45156</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>46268</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>46275</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45387</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>46235</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44979</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44998</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44517</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>46290</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45078</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>45250</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45007</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45213</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45513</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45078</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>45218</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>45178</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>45007</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>44726</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>44491</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45078</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44610</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45820</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>45728</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>46112</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>46191</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>44732</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44729</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44614</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44622</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>44501</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>44622</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44687</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44664</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44555</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>44651</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44644</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44868</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>44498</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44491</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44838</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44577</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>44691</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>44661</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>44649</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>44525</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>44622</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44613</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44588</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>44725</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>44725</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44519</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44852</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>44598</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>44692</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>44691</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>44694</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44659</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>44865</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>44715</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>44664</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>44757</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>44861</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44873</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>44661</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>44501</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>44809</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>44809</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>44813</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44810</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>44635</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44712</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>44669</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>44687</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>44728</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>44608</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>44872</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44770</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>44739</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44620</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>44687</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44635</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>44676</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>44643</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>44669</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>44482</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>44809</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>45208</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>44775</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>45621</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>45271</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>44591</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44576</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>45107</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>44991</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>45110</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>45114</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>44755</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>44783</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44560</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>45212</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45054</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45191</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>44915</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>44651</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>44643</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>44599</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>44599</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>45569</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>45574</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>45572</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44598</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45569</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>46003</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>45572</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>44706</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45253</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45146</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44768</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44651</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>45250</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>46008</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>44860</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>44987</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45895</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45895</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45895</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45895</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45230</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>44814</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>45895</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45670</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45898</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>45162</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45797</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>45797</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>44963</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45797</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>46040</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>45817</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>45909</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>45670</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45499</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>45456</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>46043</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>46043</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>45797</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>46043</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45257</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>45063</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>46048</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44746</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45734</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>45524</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45749</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45212</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>45530</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>45740</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>45632</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>46050</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45805</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45194</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45924</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>44991</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>45516</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>44511</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>46058</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>46058</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>44533</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>44555</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45931</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45063</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45561</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>46065</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>46064</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>45455</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>46064</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46065</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>45337</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44515</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>45937</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>46072</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44572</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>45544</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>45462</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>45811</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>45947</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>44770</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>45950</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>45949</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>45949</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>45948</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>44560</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>45812</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>45949</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>45904</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>45419</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44953</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>45152</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>44970</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>45093</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>46087</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>46087</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>46087</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>45960</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>45960</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>45379</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>45966</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>45358</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>45520</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>46094</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>45966</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>46098</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>45817</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>45075</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>44643</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35487,7 +35487,7 @@
         <v>45757</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35565,7 +35565,7 @@
         <v>45384</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>44664</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>44613</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>46104</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>45708</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>45813</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>45520</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>44613</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -36164,7 +36164,7 @@
         <v>45978</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>46106</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45225</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         <v>45148</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>45978</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45978</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45978</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>46108</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>45341</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>46107</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45244</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>46107</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -37065,7 +37065,7 @@
         <v>45102</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45102</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>46108</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>44894</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37367,7 +37367,7 @@
         <v>46112</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>45985</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>46112</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37586,7 +37586,7 @@
         <v>46111</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37659,7 +37659,7 @@
         <v>46112</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>46112</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>46113</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>46113</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>44496</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45572</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>45813</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>45824</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>45202</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45813</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45813</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38477,7 +38477,7 @@
         <v>44963</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38550,7 +38550,7 @@
         <v>44874</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>44896</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>44896</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>45931</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45996</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>45999</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>45831</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45187</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>45830</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>45830</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>46132</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>45833</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45102</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>46134</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>46134</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45233</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45516</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>45796</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>45813</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>44959</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -40055,7 +40055,7 @@
         <v>44991</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>45819</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>44495</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>45778</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>44950</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40440,7 +40440,7 @@
         <v>45835</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>45812</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         <v>46136</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>45079</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>45519</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>44725</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>46139</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>45433</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45807</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45842</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45337</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>46139</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45975</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>44928</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>44928</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>45621</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>46034</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45467</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>45719</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45520</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>46034</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45112</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44476</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>45770</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>45646</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>46136</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>45805</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44687</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45362</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>45760</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>44512</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>45102</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45733</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>45840</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45496</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>44591</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>45230</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -43196,7 +43196,7 @@
         <v>45174</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45040</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>45090</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45218</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45239</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>45044</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>44905</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45755</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45482</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>46104</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>46141</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -44029,7 +44029,7 @@
         <v>45759</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>46141</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -44180,7 +44180,7 @@
         <v>45358</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44631</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>46104</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>45869</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>45138</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45691</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>44943</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>44796</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>44586</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>45384</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45093</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>44973</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45394</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>46147</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45054</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>45007</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>45568</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45441,7 +45441,7 @@
         <v>46153</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>46155</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45592,7 +45592,7 @@
         <v>44993</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>46155</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45743,7 +45743,7 @@
         <v>46155</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>44732</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>46154</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>46155</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>46156</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>44655</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>45197</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45194</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>44660</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>46163</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>46163</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>45076</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45096</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>46163</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>46163</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>45123</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>45842</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -47029,7 +47029,7 @@
         <v>45751</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45762</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -47175,7 +47175,7 @@
         <v>44970</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -47248,7 +47248,7 @@
         <v>46176</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>46176</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>44726</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>44598</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>46176</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>46176</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47691,7 +47691,7 @@
         <v>46176</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47764,7 +47764,7 @@
         <v>46176</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>46176</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47910,7 +47910,7 @@
         <v>45740</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>46178</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -48061,7 +48061,7 @@
         <v>45282</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>45107</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>46181</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>46181</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>45259</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -48446,7 +48446,7 @@
         <v>46181</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48524,7 +48524,7 @@
         <v>45621</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>46182</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>46183</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>44775</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48821,7 +48821,7 @@
         <v>46183</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48894,7 +48894,7 @@
         <v>46184</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48967,7 +48967,7 @@
         <v>44523</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -49040,7 +49040,7 @@
         <v>44981</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>44803</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>44676</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>44596</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -49342,7 +49342,7 @@
         <v>46057</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>46196</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -49493,7 +49493,7 @@
         <v>45082</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>46195</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>44972</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49722,7 +49722,7 @@
         <v>45047</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>44952</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>44775</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49946,7 +49946,7 @@
         <v>46199</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>46199</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>46200</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>46200</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>45154</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>44938</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45114</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>46199</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50555,7 +50555,7 @@
         <v>46200</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50633,7 +50633,7 @@
         <v>45090</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>44525</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>46178</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50862,7 +50862,7 @@
         <v>46206</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50935,7 +50935,7 @@
         <v>46206</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -51008,7 +51008,7 @@
         <v>46206</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -51081,7 +51081,7 @@
         <v>46209</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>44512</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>46209</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -51305,7 +51305,7 @@
         <v>44890</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>46209</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>46209</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51539,7 +51539,7 @@
         <v>46209</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51617,7 +51617,7 @@
         <v>44895</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51695,7 +51695,7 @@
         <v>46209</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51773,7 +51773,7 @@
         <v>44908</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51846,7 +51846,7 @@
         <v>46211</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51919,7 +51919,7 @@
         <v>46211</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51997,7 +51997,7 @@
         <v>46211</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>44973</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -52148,7 +52148,7 @@
         <v>45702</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>44553</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45680</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>46258</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -52460,7 +52460,7 @@
         <v>46258</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>46259</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>46258</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52694,7 +52694,7 @@
         <v>44874</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>46258</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>44515</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45170</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>46217</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>45012</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -53157,7 +53157,7 @@
         <v>46217</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -53235,7 +53235,7 @@
         <v>46260</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -53313,7 +53313,7 @@
         <v>46219</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -53386,7 +53386,7 @@
         <v>45202</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -53459,7 +53459,7 @@
         <v>44586</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -53537,7 +53537,7 @@
         <v>46262</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>46219</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53688,7 +53688,7 @@
         <v>46219</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53761,7 +53761,7 @@
         <v>46181</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>46219</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53912,7 +53912,7 @@
         <v>46266</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53990,7 +53990,7 @@
         <v>46266</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54063,7 +54063,7 @@
         <v>46267</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -54141,7 +54141,7 @@
         <v>45462</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>45005</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>44715</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>45195</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -54438,7 +54438,7 @@
         <v>44609</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>44523</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>44660</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54662,7 +54662,7 @@
         <v>46063</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54735,7 +54735,7 @@
         <v>44684</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54808,7 +54808,7 @@
         <v>44602</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54886,7 +54886,7 @@
         <v>44916</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54959,7 +54959,7 @@
         <v>46274</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55037,7 +55037,7 @@
         <v>44978</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>46274</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -55193,7 +55193,7 @@
         <v>46274</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -55271,7 +55271,7 @@
         <v>46274</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>46279</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -55427,7 +55427,7 @@
         <v>46276</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -55505,7 +55505,7 @@
         <v>46276</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>44739</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55661,7 +55661,7 @@
         <v>45040</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         <v>45203</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55812,7 +55812,7 @@
         <v>46281</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55890,7 +55890,7 @@
         <v>46281</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55968,7 +55968,7 @@
         <v>45233</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56046,7 +56046,7 @@
         <v>45225</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>46239</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -56197,7 +56197,7 @@
         <v>44805</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -56270,7 +56270,7 @@
         <v>46239</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>46240</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -56421,7 +56421,7 @@
         <v>46282</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -56499,7 +56499,7 @@
         <v>46282</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>44501</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56655,7 +56655,7 @@
         <v>46240</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56733,7 +56733,7 @@
         <v>46240</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56811,7 +56811,7 @@
         <v>46240</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45617</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56962,7 +56962,7 @@
         <v>45476</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -57040,7 +57040,7 @@
         <v>45560</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>46241</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -57191,7 +57191,7 @@
         <v>44665</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -57269,7 +57269,7 @@
         <v>45142</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -57347,7 +57347,7 @@
         <v>46287</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -57420,7 +57420,7 @@
         <v>46286</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -57493,7 +57493,7 @@
         <v>45076</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>46246</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>46245</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57727,7 +57727,7 @@
         <v>46246</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57805,7 +57805,7 @@
         <v>46245</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57883,7 +57883,7 @@
         <v>45072</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57956,7 +57956,7 @@
         <v>44591</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
         <v>45455</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58112,7 +58112,7 @@
         <v>46289</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58185,7 +58185,7 @@
         <v>45089</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -58258,7 +58258,7 @@
         <v>46293</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -58336,7 +58336,7 @@
         <v>44909</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -58409,7 +58409,7 @@
         <v>46290</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -58482,7 +58482,7 @@
         <v>44824</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>44890</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -58638,7 +58638,7 @@
         <v>44923</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58716,7 +58716,7 @@
         <v>44977</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58794,7 +58794,7 @@
         <v>46289</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58867,7 +58867,7 @@
         <v>44795</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>46252</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -59023,7 +59023,7 @@
         <v>45621</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59101,7 +59101,7 @@
         <v>45621</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59179,7 +59179,7 @@
         <v>45621</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59257,7 +59257,7 @@
         <v>46056</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -59335,7 +59335,7 @@
         <v>46056</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         <v>44949</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -59486,7 +59486,7 @@
         <v>45176</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -59559,7 +59559,7 @@
         <v>46279</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -59637,7 +59637,7 @@
         <v>45740</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59710,7 +59710,7 @@
         <v>44998</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59783,7 +59783,7 @@
         <v>46253</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59856,7 +59856,7 @@
         <v>44522</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59929,7 +59929,7 @@
         <v>44536</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -60002,7 +60002,7 @@
         <v>44578</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60075,7 +60075,7 @@
         <v>45213</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60148,7 +60148,7 @@
         <v>44810</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60221,7 +60221,7 @@
         <v>45259</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -60294,7 +60294,7 @@
         <v>44841</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -60367,7 +60367,7 @@
         <v>44550</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>45337</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -60513,7 +60513,7 @@
         <v>44923</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>45225</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -60664,7 +60664,7 @@
         <v>44953</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60737,7 +60737,7 @@
         <v>44552</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60810,7 +60810,7 @@
         <v>45467</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>45147</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>44783</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -61039,7 +61039,7 @@
         <v>44973</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61117,7 +61117,7 @@
         <v>44972</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61195,7 +61195,7 @@
         <v>45687</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61268,7 +61268,7 @@
         <v>44725</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -61341,7 +61341,7 @@
         <v>45040</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -61414,7 +61414,7 @@
         <v>44915</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -61487,7 +61487,7 @@
         <v>45097</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -61560,7 +61560,7 @@
         <v>44531</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -61638,7 +61638,7 @@
         <v>45468</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>44496</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>44938</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>45597</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45562</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>45538</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62086,7 +62086,7 @@
         <v>45520</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>45569</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45013</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>45546</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -62388,7 +62388,7 @@
         <v>44964</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -62461,7 +62461,7 @@
         <v>45078</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -62534,7 +62534,7 @@
         <v>45428</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>45428</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62680,7 +62680,7 @@
         <v>44729</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62758,7 +62758,7 @@
         <v>45390</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62836,7 +62836,7 @@
         <v>44672</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62909,7 +62909,7 @@
         <v>45182</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62987,7 +62987,7 @@
         <v>45916</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -63060,7 +63060,7 @@
         <v>45957</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -63133,7 +63133,7 @@
         <v>46034</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>46089</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>46204</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>45114</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45106</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>46132</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45590</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>45061</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>45063</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45660</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>43955</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>46132</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>45439</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>46030</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>46183</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45106</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>46279</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>46205</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>44918</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>45182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>46009</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>46196</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>46132</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>45210</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>44865</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45681</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44662</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>44482</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45660</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45622</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>45076</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45947</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>44771</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>45190</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>46205</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44935</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>45796</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>45891</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44644</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>45226</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>44194</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45076</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>44636</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>46170</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>44474</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>46071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>45840</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>44837</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>45362</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>45520</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45198</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>45160</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>44588</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>44779</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>44739</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>45238</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>44727</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>45205</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>44819</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>44511</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44684</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>44874</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>45412</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>44728</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>45078</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>46265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44525</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>45107</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>45315</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>46048</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45070</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>44984</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>45999</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44858</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45545</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>45699</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>45390</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>44874</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>45460</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>46121</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45999</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>45372</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>44903</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>46161</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>44683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44729</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>45446</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>45274</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>45895</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>46089</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44495</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>44515</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>44578</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44778</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45068</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>45045</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45393</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>45425</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45951</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>45775</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45583</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>46001</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>44644</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>46142</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45743</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45063</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>44883</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45063</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>46287</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>46252</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>44782</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44859</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>44687</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44813</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44622</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>44501</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>44715</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         <v>44792</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>44509</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>44606</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>45154</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45896</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>46056</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>46062</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>45329</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>46098</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45678</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>46063</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>45695</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>44607</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>45831</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>44985</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>46139</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44712</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45384</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>45160</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>46154</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>45436</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44915</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>45013</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>46195</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>46195</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>44572</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44991</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>44875</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45162</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>46211</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>46211</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>46259</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>46002</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45135</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>46260</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45156</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>46268</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>46275</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45387</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>46235</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44979</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44998</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44517</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>46290</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45078</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>45250</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45007</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45213</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45513</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45078</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>45218</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>45178</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>45007</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>44726</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>44491</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45078</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44610</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45820</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>45728</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>46112</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>46191</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>44732</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44729</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44614</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44622</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>44501</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>44622</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44687</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44664</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44555</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>44651</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44644</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44868</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>44498</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44491</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44838</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44577</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>44691</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>44661</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>44649</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>44525</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>44622</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44613</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44588</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>44725</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>44725</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44519</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44852</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>44598</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>44692</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>44691</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>44694</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44659</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>44865</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>44715</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>44664</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>44757</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>44861</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44873</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>44661</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>44501</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>44809</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>44809</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>44813</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44810</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>44635</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44712</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>44669</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>44687</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>44728</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>44608</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>44872</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44770</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>44739</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44620</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>44687</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44635</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>44676</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>44643</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>44669</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>44482</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>44809</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>45208</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>44775</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>45621</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>45271</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>44591</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44576</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>45107</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>44991</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>45110</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>45114</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>44755</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>44783</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44560</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>45212</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45054</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45191</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>44915</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>44651</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>44643</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>44599</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>44599</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>45569</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>45574</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>45572</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44598</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45569</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>46003</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>45572</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>44706</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45253</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45146</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44768</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44651</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>45250</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>46008</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>44860</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>44987</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45895</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45895</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45895</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45895</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45230</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>44814</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>45895</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45670</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45898</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>45162</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45797</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>45797</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>44963</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45797</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>46040</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>45817</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>45909</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>45670</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45499</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>45456</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>46043</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>46043</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>45797</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>46043</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45257</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>45063</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>46048</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44746</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45734</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>45524</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45749</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45212</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>45530</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>45740</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>45632</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>46050</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45805</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45194</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45924</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>44991</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>45516</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>44511</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>46058</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>46058</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>44533</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>44555</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45931</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45063</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45561</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>46065</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>46064</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>45455</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>46064</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46065</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>45337</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44515</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>45937</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>46072</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44572</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>45544</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>45462</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>45811</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>45947</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>44770</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>45950</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>45949</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>45949</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>45948</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>44560</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>45812</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>45949</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>45904</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>45419</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44953</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>45152</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>44970</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>45093</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>46087</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>46087</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>46087</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>45960</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>45960</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>45379</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>45966</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>45358</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>45520</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>46094</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>45966</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>46098</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>45817</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>45075</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>44643</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35487,7 +35487,7 @@
         <v>45757</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35565,7 +35565,7 @@
         <v>45384</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>44664</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>44613</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>46104</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>45708</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>45813</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>45520</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>44613</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -36164,7 +36164,7 @@
         <v>45978</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>46106</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45225</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         <v>45148</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>45978</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45978</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45978</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>46108</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>45341</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>46107</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45244</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>46107</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -37065,7 +37065,7 @@
         <v>45102</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45102</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>46108</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>44894</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37367,7 +37367,7 @@
         <v>46112</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>45985</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>46112</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37586,7 +37586,7 @@
         <v>46111</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37659,7 +37659,7 @@
         <v>46112</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>46112</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>46113</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>46113</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>44496</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45572</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>45813</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>45824</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>45202</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45813</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45813</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38477,7 +38477,7 @@
         <v>44963</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38550,7 +38550,7 @@
         <v>44874</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>44896</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>44896</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>45931</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45996</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>45999</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>45831</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45187</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>45830</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>45830</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>46132</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>45833</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45102</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>46134</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>46134</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45233</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45516</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>45796</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>45813</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>44959</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -40055,7 +40055,7 @@
         <v>44991</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>45819</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>44495</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>45778</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>44950</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40440,7 +40440,7 @@
         <v>45835</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>45812</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         <v>46136</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>45079</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>45519</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>44725</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>46139</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>45433</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45807</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45842</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45337</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>46139</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45975</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>44928</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>44928</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>45621</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>46034</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45467</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>45719</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45520</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>46034</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45112</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44476</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>45770</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>45646</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>46136</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>45805</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44687</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45362</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>45760</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>44512</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>45102</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45733</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>45840</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45496</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>44591</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>45230</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -43196,7 +43196,7 @@
         <v>45174</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45040</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>45090</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45218</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45239</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>45044</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>44905</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45755</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45482</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>46104</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>46141</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -44029,7 +44029,7 @@
         <v>45759</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>46141</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -44180,7 +44180,7 @@
         <v>45358</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44631</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>46104</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>45869</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>45138</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45691</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>44943</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>44796</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>44586</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>45384</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45093</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>44973</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45394</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>46147</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45054</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>45007</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>45568</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45441,7 +45441,7 @@
         <v>46153</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>46155</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45592,7 +45592,7 @@
         <v>44993</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>46155</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45743,7 +45743,7 @@
         <v>46155</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>44732</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>46154</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>46155</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>46156</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>44655</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>45197</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45194</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>44660</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>46163</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>46163</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>45076</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45096</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>46163</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>46163</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>45123</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>45842</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -47029,7 +47029,7 @@
         <v>45751</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45762</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -47175,7 +47175,7 @@
         <v>44970</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -47248,7 +47248,7 @@
         <v>46176</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>46176</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>44726</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>44598</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>46176</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>46176</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47691,7 +47691,7 @@
         <v>46176</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47764,7 +47764,7 @@
         <v>46176</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>46176</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47910,7 +47910,7 @@
         <v>45740</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>46178</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -48061,7 +48061,7 @@
         <v>45282</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>45107</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>46181</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>46181</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>45259</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -48446,7 +48446,7 @@
         <v>46181</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48524,7 +48524,7 @@
         <v>45621</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>46182</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>46183</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>44775</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48821,7 +48821,7 @@
         <v>46183</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48894,7 +48894,7 @@
         <v>46184</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48967,7 +48967,7 @@
         <v>44523</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -49040,7 +49040,7 @@
         <v>44981</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>44803</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>44676</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>44596</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -49342,7 +49342,7 @@
         <v>46057</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>46196</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -49493,7 +49493,7 @@
         <v>45082</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>46195</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>44972</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49722,7 +49722,7 @@
         <v>45047</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>44952</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>44775</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49946,7 +49946,7 @@
         <v>46199</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>46199</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>46200</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>46200</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>45154</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>44938</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45114</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>46199</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50555,7 +50555,7 @@
         <v>46200</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50633,7 +50633,7 @@
         <v>45090</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>44525</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>46178</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50862,7 +50862,7 @@
         <v>46206</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50935,7 +50935,7 @@
         <v>46206</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -51008,7 +51008,7 @@
         <v>46206</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -51081,7 +51081,7 @@
         <v>46209</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>44512</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>46209</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -51305,7 +51305,7 @@
         <v>44890</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>46209</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>46209</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51539,7 +51539,7 @@
         <v>46209</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51617,7 +51617,7 @@
         <v>44895</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51695,7 +51695,7 @@
         <v>46209</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51773,7 +51773,7 @@
         <v>44908</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51846,7 +51846,7 @@
         <v>46211</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51919,7 +51919,7 @@
         <v>46211</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51997,7 +51997,7 @@
         <v>46211</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>44973</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -52148,7 +52148,7 @@
         <v>45702</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>44553</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45680</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>46258</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -52460,7 +52460,7 @@
         <v>46258</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>46259</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>46258</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52694,7 +52694,7 @@
         <v>44874</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>46258</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>44515</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45170</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>46217</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>45012</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -53157,7 +53157,7 @@
         <v>46217</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -53235,7 +53235,7 @@
         <v>46260</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -53313,7 +53313,7 @@
         <v>46219</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -53386,7 +53386,7 @@
         <v>45202</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -53459,7 +53459,7 @@
         <v>44586</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -53537,7 +53537,7 @@
         <v>46262</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>46219</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53688,7 +53688,7 @@
         <v>46219</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53761,7 +53761,7 @@
         <v>46181</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>46219</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53912,7 +53912,7 @@
         <v>46266</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53990,7 +53990,7 @@
         <v>46266</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54063,7 +54063,7 @@
         <v>46267</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -54141,7 +54141,7 @@
         <v>45462</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>45005</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>44715</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>45195</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -54438,7 +54438,7 @@
         <v>44609</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>44523</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>44660</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54662,7 +54662,7 @@
         <v>46063</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54735,7 +54735,7 @@
         <v>44684</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54808,7 +54808,7 @@
         <v>44602</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54886,7 +54886,7 @@
         <v>44916</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54959,7 +54959,7 @@
         <v>46274</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55037,7 +55037,7 @@
         <v>44978</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>46274</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -55193,7 +55193,7 @@
         <v>46274</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -55271,7 +55271,7 @@
         <v>46274</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>46279</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -55427,7 +55427,7 @@
         <v>46276</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -55505,7 +55505,7 @@
         <v>46276</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>44739</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55661,7 +55661,7 @@
         <v>45040</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         <v>45203</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55812,7 +55812,7 @@
         <v>46281</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55890,7 +55890,7 @@
         <v>46281</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55968,7 +55968,7 @@
         <v>45233</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56046,7 +56046,7 @@
         <v>45225</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>46239</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -56197,7 +56197,7 @@
         <v>44805</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -56270,7 +56270,7 @@
         <v>46239</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>46240</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -56421,7 +56421,7 @@
         <v>46282</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -56499,7 +56499,7 @@
         <v>46282</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>44501</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56655,7 +56655,7 @@
         <v>46240</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56733,7 +56733,7 @@
         <v>46240</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56811,7 +56811,7 @@
         <v>46240</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45617</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56962,7 +56962,7 @@
         <v>45476</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -57040,7 +57040,7 @@
         <v>45560</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>46241</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -57191,7 +57191,7 @@
         <v>44665</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -57269,7 +57269,7 @@
         <v>45142</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -57347,7 +57347,7 @@
         <v>46287</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -57420,7 +57420,7 @@
         <v>46286</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -57493,7 +57493,7 @@
         <v>45076</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>46246</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>46245</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57727,7 +57727,7 @@
         <v>46246</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57805,7 +57805,7 @@
         <v>46245</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57883,7 +57883,7 @@
         <v>45072</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57956,7 +57956,7 @@
         <v>44591</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
         <v>45455</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58112,7 +58112,7 @@
         <v>46289</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58185,7 +58185,7 @@
         <v>45089</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -58258,7 +58258,7 @@
         <v>46293</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -58336,7 +58336,7 @@
         <v>44909</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -58409,7 +58409,7 @@
         <v>46290</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -58482,7 +58482,7 @@
         <v>44824</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>44890</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -58638,7 +58638,7 @@
         <v>44923</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58716,7 +58716,7 @@
         <v>44977</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58794,7 +58794,7 @@
         <v>46289</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58867,7 +58867,7 @@
         <v>44795</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>46252</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -59023,7 +59023,7 @@
         <v>45621</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59101,7 +59101,7 @@
         <v>45621</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59179,7 +59179,7 @@
         <v>45621</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59257,7 +59257,7 @@
         <v>46056</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -59335,7 +59335,7 @@
         <v>46056</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         <v>44949</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -59486,7 +59486,7 @@
         <v>45176</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -59559,7 +59559,7 @@
         <v>46279</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -59637,7 +59637,7 @@
         <v>45740</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59710,7 +59710,7 @@
         <v>44998</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59783,7 +59783,7 @@
         <v>46253</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59856,7 +59856,7 @@
         <v>44522</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59929,7 +59929,7 @@
         <v>44536</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -60002,7 +60002,7 @@
         <v>44578</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60075,7 +60075,7 @@
         <v>45213</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60148,7 +60148,7 @@
         <v>44810</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60221,7 +60221,7 @@
         <v>45259</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -60294,7 +60294,7 @@
         <v>44841</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -60367,7 +60367,7 @@
         <v>44550</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>45337</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -60513,7 +60513,7 @@
         <v>44923</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>45225</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -60664,7 +60664,7 @@
         <v>44953</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60737,7 +60737,7 @@
         <v>44552</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60810,7 +60810,7 @@
         <v>45467</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>45147</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>44783</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -61039,7 +61039,7 @@
         <v>44973</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61117,7 +61117,7 @@
         <v>44972</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61195,7 +61195,7 @@
         <v>45687</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61268,7 +61268,7 @@
         <v>44725</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -61341,7 +61341,7 @@
         <v>45040</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -61414,7 +61414,7 @@
         <v>44915</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -61487,7 +61487,7 @@
         <v>45097</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -61560,7 +61560,7 @@
         <v>44531</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -61638,7 +61638,7 @@
         <v>45468</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>44496</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>44938</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>45597</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45562</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>45538</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62086,7 +62086,7 @@
         <v>45520</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>45569</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45013</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>45546</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -62388,7 +62388,7 @@
         <v>44964</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -62461,7 +62461,7 @@
         <v>45078</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -62534,7 +62534,7 @@
         <v>45428</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>45428</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62680,7 +62680,7 @@
         <v>44729</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62758,7 +62758,7 @@
         <v>45390</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62836,7 +62836,7 @@
         <v>44672</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62909,7 +62909,7 @@
         <v>45182</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62987,7 +62987,7 @@
         <v>45916</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -63060,7 +63060,7 @@
         <v>45957</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -63133,7 +63133,7 @@
         <v>46034</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>46089</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>46204</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>45114</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45106</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>46132</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>46196</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>45590</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>45659</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>45061</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>45660</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>43955</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>46132</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>46030</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45439</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>45106</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>46183</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>46279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45182</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>46205</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>44918</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>46009</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>46132</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>45210</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>44865</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44662</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44482</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>45076</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45660</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>45622</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45190</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>45947</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>44771</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>46205</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44935</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>45796</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>44644</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45226</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45891</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>44194</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>45076</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44636</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>46170</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>45362</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>44837</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>45198</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>45520</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>45840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>46071</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>44588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>45160</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>44779</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44727</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>45205</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>44739</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>45238</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>46132</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44819</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>44511</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>44684</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>44874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>45412</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>45107</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44728</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45078</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>44525</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>46265</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>45315</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44984</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>45545</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>44858</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>45070</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>45999</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>46048</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45699</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>45390</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>44874</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>45446</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>44683</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>44903</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>45372</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45460</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>44729</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>46121</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>45999</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>46161</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>46282</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45274</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>45895</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>46089</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>44495</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>44515</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>44578</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>44778</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45775</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>45063</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>45068</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>45425</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>44883</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>45393</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>44644</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>45583</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45951</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>45045</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>46001</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45063</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>46142</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45743</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>46287</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>46252</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>46300</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>44782</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44859</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>44687</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44813</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>44622</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>44501</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>44715</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>44792</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45013</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>44991</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45695</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45250</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>45154</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>45078</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>44998</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>45896</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45160</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>45329</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>44875</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>45384</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45436</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45156</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45678</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>44509</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44517</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>44606</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>45513</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44572</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>45387</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45162</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>44712</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>46098</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>44607</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45213</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>44979</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>46063</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>45007</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>45831</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>44915</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>46139</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44985</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>46056</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>46062</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>46154</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>46195</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>46195</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>46211</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>46002</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45135</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>46268</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>46275</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>46235</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>46290</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19699,7 +19699,7 @@
         <v>46259</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>46260</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>44726</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44610</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45078</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45218</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>45178</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45007</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>44491</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45078</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45820</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45728</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>46112</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>46191</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>44555</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>44614</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44729</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44732</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>44622</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>44501</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44622</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44687</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>44664</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>44651</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>44644</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44868</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>44498</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>44491</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>44838</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>44577</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44691</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>44661</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>44649</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>44525</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>44622</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>44613</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44588</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>44725</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44725</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>44519</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>44852</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44598</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>44873</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44669</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>44692</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44620</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>44661</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>44691</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44694</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44659</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44635</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>44501</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>44809</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44687</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>44687</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44865</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>44809</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>44715</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44813</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>44664</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>44608</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>44728</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>44810</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>44676</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>44757</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>44872</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>44635</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>44861</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>44712</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>44770</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>44739</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44643</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45233</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>44669</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>44860</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>45102</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>45259</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>45419</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>45646</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45047</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45152</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45044</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45384</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45089</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45102</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>44814</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44523</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44725</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44726</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>45090</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>45213</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>45054</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>45142</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>45560</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>44578</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>45218</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>44775</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>45040</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>44928</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>44928</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45433</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>45394</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45102</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>45462</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>45379</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>44890</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45170</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>44963</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44987</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>44953</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>45467</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>44768</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>45519</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>45040</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>44522</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>44959</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>45072</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>45257</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>45138</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>44991</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>44824</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>45063</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>45075</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>44909</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>44894</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>44973</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45358</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>45147</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44715</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>45530</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44890</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>44482</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>44550</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>45162</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44972</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45482</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>44560</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>44970</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>44809</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>45895</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>45895</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>45895</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>45895</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>45895</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>44981</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>45898</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>45621</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>45797</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31251,7 +31251,7 @@
         <v>44512</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>44978</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>45337</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>45093</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>44916</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>44525</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>45797</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>45621</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>45516</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45516</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>45123</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>45520</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>44915</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>45797</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
         <v>44973</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>44560</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>45817</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>44972</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32610,7 +32610,7 @@
         <v>44977</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>45225</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32761,7 +32761,7 @@
         <v>45597</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32834,7 +32834,7 @@
         <v>45909</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32907,7 +32907,7 @@
         <v>44938</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>44874</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44553</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>45562</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>44586</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45063</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45544</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44552</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>45670</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44665</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33667,7 +33667,7 @@
         <v>45476</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         <v>45114</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>44536</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45079</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>44896</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -34042,7 +34042,7 @@
         <v>44896</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>45148</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>45574</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>45538</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>45253</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -34417,7 +34417,7 @@
         <v>44952</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>45569</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>45546</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>45572</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>44598</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>45146</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>45569</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45569</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>45468</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>45572</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>44591</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>45924</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>44501</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35391,7 +35391,7 @@
         <v>44555</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>45013</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>45740</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>45520</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45572</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45097</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>44923</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>45191</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45341</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -36063,7 +36063,7 @@
         <v>44598</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>45107</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36219,7 +36219,7 @@
         <v>44599</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44938</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36365,7 +36365,7 @@
         <v>44602</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45202</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>45456</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>44643</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45670</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>45499</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>44915</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>44533</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>45931</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>45797</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>44943</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>45225</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>45384</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>45749</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>45524</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37485,7 +37485,7 @@
         <v>45740</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>45937</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>45734</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>45082</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37782,7 +37782,7 @@
         <v>45632</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44795</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37933,7 +37933,7 @@
         <v>45805</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>44775</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>45197</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>45621</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>44805</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>45230</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45230</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38449,7 +38449,7 @@
         <v>44725</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>44706</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>44651</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>44609</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45687</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>45812</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>45239</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>45811</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>45708</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>44643</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>45817</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45195</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45950</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>44732</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>45949</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>44923</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>45114</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>45813</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>45947</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>44783</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>45949</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>45949</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>44684</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45824</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45948</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>45093</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>45455</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44591</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40558,7 +40558,7 @@
         <v>44631</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>45358</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>44895</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>45830</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40865,7 +40865,7 @@
         <v>45830</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40938,7 +40938,7 @@
         <v>44991</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -41016,7 +41016,7 @@
         <v>45202</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -41089,7 +41089,7 @@
         <v>45680</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -41167,7 +41167,7 @@
         <v>45904</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45831</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41313,7 +41313,7 @@
         <v>45012</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>44496</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>45960</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45960</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45833</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>44664</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45271</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41839,7 +41839,7 @@
         <v>44746</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41912,7 +41912,7 @@
         <v>44660</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>44651</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>44810</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>45617</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>45176</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42287,7 +42287,7 @@
         <v>45966</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45966</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45455</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>44783</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>45174</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>45212</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>45757</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>45194</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42901,7 +42901,7 @@
         <v>45233</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42979,7 +42979,7 @@
         <v>45621</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -43057,7 +43057,7 @@
         <v>45621</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>45621</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45842</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45807</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45102</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>45187</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43515,7 +43515,7 @@
         <v>45702</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45005</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>44770</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45719</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>44803</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>45467</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>44841</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>45770</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>44755</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>44687</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45076</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45755</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>45225</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45759</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>45978</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>45978</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45362</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44786,7 +44786,7 @@
         <v>44775</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44859,7 +44859,7 @@
         <v>45203</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45978</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>45869</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45978</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45007</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>44796</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44613</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45054</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>45337</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>44495</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>45110</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>44970</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45259</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>44991</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>44496</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45984,7 +45984,7 @@
         <v>46098</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>45208</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>46104</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>45250</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>45985</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45520</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>44531</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46505,7 +46505,7 @@
         <v>46106</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>46111</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>46108</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>46108</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>45212</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>46113</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>46112</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>46113</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>45496</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>46112</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>46112</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -47318,7 +47318,7 @@
         <v>44596</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>46112</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>45520</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>44586</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>44973</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>44993</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>45996</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>45999</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47917,7 +47917,7 @@
         <v>45040</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>44874</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>44572</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>46134</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -48214,7 +48214,7 @@
         <v>46003</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>46134</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>44949</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>44953</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48511,7 +48511,7 @@
         <v>45112</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>46136</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>44739</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>45840</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>44613</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>46136</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>46008</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45462</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>45796</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>44512</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>44905</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45090</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>45244</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>44523</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45107</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>44511</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>45819</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>45778</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45805</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>45733</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>45282</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -50084,7 +50084,7 @@
         <v>44515</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>46034</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>44576</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>45975</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -50386,7 +50386,7 @@
         <v>44655</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>45760</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>44998</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45561</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>44660</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50766,7 +50766,7 @@
         <v>44963</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50839,7 +50839,7 @@
         <v>45691</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50912,7 +50912,7 @@
         <v>44515</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>46040</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45154</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>46043</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>44599</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>45835</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>44950</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -51438,7 +51438,7 @@
         <v>45812</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>45194</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>46043</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>46048</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>46139</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>46034</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51886,7 +51886,7 @@
         <v>45337</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>45568</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>46139</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>44908</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -52178,7 +52178,7 @@
         <v>46050</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -52256,7 +52256,7 @@
         <v>44591</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>46141</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -52407,7 +52407,7 @@
         <v>46104</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -52485,7 +52485,7 @@
         <v>46104</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52563,7 +52563,7 @@
         <v>46141</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52641,7 +52641,7 @@
         <v>46064</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52714,7 +52714,7 @@
         <v>46064</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52787,7 +52787,7 @@
         <v>46065</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52865,7 +52865,7 @@
         <v>46065</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52943,7 +52943,7 @@
         <v>46147</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53016,7 +53016,7 @@
         <v>46153</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -53089,7 +53089,7 @@
         <v>46072</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -53167,7 +53167,7 @@
         <v>46155</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -53240,7 +53240,7 @@
         <v>46155</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -53318,7 +53318,7 @@
         <v>46155</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>46087</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -53474,7 +53474,7 @@
         <v>46155</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>46087</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53630,7 +53630,7 @@
         <v>46087</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53708,7 +53708,7 @@
         <v>45076</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53781,7 +53781,7 @@
         <v>45096</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53859,7 +53859,7 @@
         <v>46163</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53932,7 +53932,7 @@
         <v>46163</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>46163</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -54078,7 +54078,7 @@
         <v>45762</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -54151,7 +54151,7 @@
         <v>45842</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         <v>45751</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -54297,7 +54297,7 @@
         <v>46176</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -54370,7 +54370,7 @@
         <v>46176</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -54443,7 +54443,7 @@
         <v>46176</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54516,7 +54516,7 @@
         <v>46176</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54589,7 +54589,7 @@
         <v>45740</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54662,7 +54662,7 @@
         <v>46176</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54735,7 +54735,7 @@
         <v>46176</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54808,7 +54808,7 @@
         <v>46181</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54886,7 +54886,7 @@
         <v>46182</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54959,7 +54959,7 @@
         <v>46183</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55032,7 +55032,7 @@
         <v>46183</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -55105,7 +55105,7 @@
         <v>46184</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>46057</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -55251,7 +55251,7 @@
         <v>46195</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -55329,7 +55329,7 @@
         <v>46196</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -55407,7 +55407,7 @@
         <v>46200</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -55485,7 +55485,7 @@
         <v>46200</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55563,7 +55563,7 @@
         <v>46200</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55641,7 +55641,7 @@
         <v>46199</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55719,7 +55719,7 @@
         <v>46199</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55797,7 +55797,7 @@
         <v>46209</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55875,7 +55875,7 @@
         <v>46209</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55953,7 +55953,7 @@
         <v>46206</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56026,7 +56026,7 @@
         <v>46206</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -56099,7 +56099,7 @@
         <v>46209</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>46209</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -56255,7 +56255,7 @@
         <v>46209</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -56328,7 +56328,7 @@
         <v>46206</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -56401,7 +56401,7 @@
         <v>46209</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -56479,7 +56479,7 @@
         <v>46211</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56552,7 +56552,7 @@
         <v>46211</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>46217</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56708,7 +56708,7 @@
         <v>46217</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56786,7 +56786,7 @@
         <v>46219</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56859,7 +56859,7 @@
         <v>46219</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>46219</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57010,7 +57010,7 @@
         <v>46181</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>46219</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -57156,7 +57156,7 @@
         <v>46266</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>46266</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>46267</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -57385,7 +57385,7 @@
         <v>46274</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -57463,7 +57463,7 @@
         <v>46063</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57536,7 +57536,7 @@
         <v>46274</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57614,7 +57614,7 @@
         <v>46274</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57692,7 +57692,7 @@
         <v>46274</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57770,7 +57770,7 @@
         <v>46276</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57848,7 +57848,7 @@
         <v>46276</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57926,7 +57926,7 @@
         <v>46279</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58004,7 +58004,7 @@
         <v>46239</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58082,7 +58082,7 @@
         <v>46281</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -58160,7 +58160,7 @@
         <v>46281</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>46282</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -58316,7 +58316,7 @@
         <v>46239</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -58394,7 +58394,7 @@
         <v>46240</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -58467,7 +58467,7 @@
         <v>46286</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -58540,7 +58540,7 @@
         <v>46240</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58618,7 +58618,7 @@
         <v>46240</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58696,7 +58696,7 @@
         <v>46240</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58774,7 +58774,7 @@
         <v>46241</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58852,7 +58852,7 @@
         <v>46287</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         <v>46245</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         <v>46246</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59081,7 +59081,7 @@
         <v>46246</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59159,7 +59159,7 @@
         <v>46289</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -59232,7 +59232,7 @@
         <v>46290</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -59305,7 +59305,7 @@
         <v>46293</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -59383,7 +59383,7 @@
         <v>46252</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -59461,7 +59461,7 @@
         <v>46289</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -59534,7 +59534,7 @@
         <v>46253</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59607,7 +59607,7 @@
         <v>46279</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59685,7 +59685,7 @@
         <v>46300</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59763,7 +59763,7 @@
         <v>46176</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59836,7 +59836,7 @@
         <v>46300</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>46300</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59987,7 +59987,7 @@
         <v>46300</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60065,7 +60065,7 @@
         <v>46300</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>46300</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -60221,7 +60221,7 @@
         <v>46178</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -60299,7 +60299,7 @@
         <v>46181</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>46056</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         <v>46056</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -60533,7 +60533,7 @@
         <v>45813</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>46043</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60684,7 +60684,7 @@
         <v>46258</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60762,7 +60762,7 @@
         <v>46258</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60840,7 +60840,7 @@
         <v>46259</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60918,7 +60918,7 @@
         <v>46258</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60996,7 +60996,7 @@
         <v>46258</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61074,7 +61074,7 @@
         <v>45813</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61152,7 +61152,7 @@
         <v>45931</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61225,7 +61225,7 @@
         <v>46260</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -61303,7 +61303,7 @@
         <v>46304</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -61381,7 +61381,7 @@
         <v>46304</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -61459,7 +61459,7 @@
         <v>46199</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -61532,7 +61532,7 @@
         <v>46262</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -61610,7 +61610,7 @@
         <v>46245</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61688,7 +61688,7 @@
         <v>46154</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61766,7 +61766,7 @@
         <v>46156</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61844,7 +61844,7 @@
         <v>44729</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61922,7 +61922,7 @@
         <v>44672</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61995,7 +61995,7 @@
         <v>44964</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62068,7 +62068,7 @@
         <v>45078</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62141,7 +62141,7 @@
         <v>45428</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62214,7 +62214,7 @@
         <v>45428</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62287,7 +62287,7 @@
         <v>45390</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -62365,7 +62365,7 @@
         <v>45182</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -62443,7 +62443,7 @@
         <v>45916</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -62516,7 +62516,7 @@
         <v>45957</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -62589,7 +62589,7 @@
         <v>46034</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>46089</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62745,7 +62745,7 @@
         <v>46296</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>46204</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>45114</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45106</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>46132</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>46196</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>45590</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>45061</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>45660</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>43955</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>46132</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45439</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>46030</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>46183</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45106</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>46279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45182</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>46205</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>44918</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>46009</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>46132</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>45210</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>44865</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44662</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>45660</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45622</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44938</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>45076</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>45947</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44771</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45190</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>46205</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>44935</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45796</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>44644</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45226</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>45891</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>44194</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45076</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>44636</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>46170</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>45840</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>44837</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>45362</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45520</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45198</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45160</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>44588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44779</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44739</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>45238</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>44727</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>46132</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45205</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>44819</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>44511</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44684</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>44874</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>44728</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45078</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44525</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>45107</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>45412</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>46265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>45315</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>45070</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>44984</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>45999</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>46048</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>44858</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>45545</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>45699</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45390</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44874</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>45372</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>44903</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>46161</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45999</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>46121</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>44683</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>44729</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>45446</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>46282</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45460</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45274</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>45895</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>46089</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>44495</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>44515</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>44578</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>44778</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45068</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45045</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45425</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45583</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>45775</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>46142</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44644</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45951</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>46001</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>45743</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>45063</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44883</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45063</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>46287</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>46252</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>46300</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45393</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>44782</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>44859</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44687</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>44813</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>44622</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44501</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>44792</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>44715</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>44606</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>45154</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>45678</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45329</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>45896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45831</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>44985</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>46139</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45695</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44607</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44712</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>46154</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45384</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>45160</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>45436</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>44915</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>45013</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>46056</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>46062</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>44572</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>44991</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44875</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45162</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>46098</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>46195</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>46195</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>45156</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>46063</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>45387</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>44979</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>44998</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>46211</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>44517</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>46002</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>45135</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>46275</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>46235</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>45078</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>45250</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>46290</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45007</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>45213</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>45513</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>44509</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>46259</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>46260</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>46268</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45078</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45218</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45178</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>45007</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>44726</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>44491</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>45078</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44610</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45820</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45728</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>46112</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>46191</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>44732</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>44614</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>44729</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>44622</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44501</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>44622</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>44687</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>44664</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>44651</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44644</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>44555</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>44868</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44498</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>44491</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>44838</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>44691</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>44577</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>44661</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>44525</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44649</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>44622</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44613</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44588</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44725</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>44725</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44852</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>44519</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>44598</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>44692</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>44691</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>44694</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>44659</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44715</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>44865</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>44664</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>44757</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44861</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44873</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>44661</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44501</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>44809</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>44809</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>44813</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>44810</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>44635</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44712</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>44669</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>44687</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>44728</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>44608</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>44872</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>44770</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>44739</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>44620</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>44635</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>44687</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>44676</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>44643</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44669</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>44809</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>44576</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>45114</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>44560</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45208</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>44775</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45107</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45621</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45271</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>44991</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44591</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>45054</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44755</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>44783</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45212</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>45110</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>45191</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>44915</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>44651</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>44643</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>44599</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>44599</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>44706</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44651</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>45250</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>44768</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45146</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44860</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45230</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>44987</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>44814</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45670</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45162</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44963</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>45257</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -28166,7 +28166,7 @@
         <v>44746</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>45194</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -28317,7 +28317,7 @@
         <v>45212</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -28395,7 +28395,7 @@
         <v>45530</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44991</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45516</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>44511</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>45063</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45561</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45455</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44533</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>44515</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>45337</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         <v>44555</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>45544</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45462</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44572</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>44770</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>44560</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45419</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>44953</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>44970</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45152</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>45093</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>45379</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45358</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>45520</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>45075</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -30290,7 +30290,7 @@
         <v>45757</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>44643</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>44664</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>44613</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45384</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45520</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>44613</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45225</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45148</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45244</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45102</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>45102</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>44894</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>45341</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>46139</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>45337</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>46139</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45975</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>44496</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45572</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>46034</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45202</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>46034</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44963</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>44874</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>46136</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>44896</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32286,7 +32286,7 @@
         <v>44896</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>45805</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45760</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45895</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45895</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>45895</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45895</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>45187</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45895</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44512</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>45733</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>45840</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>45898</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45102</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>46104</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>46141</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>45233</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>46141</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>46104</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33718,7 +33718,7 @@
         <v>45516</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>45797</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45797</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
         <v>45797</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>44959</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>44991</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -34171,7 +34171,7 @@
         <v>45817</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>44495</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45909</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44950</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45079</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>45519</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>45063</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>44725</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>45433</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>44928</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>44928</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>45621</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>45520</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>46147</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45924</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>45112</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45646</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>45931</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>46153</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         <v>44687</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45362</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>45937</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45102</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>45496</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44591</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45230</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>46155</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45174</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>45040</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>45090</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>45947</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45218</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45239</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>45044</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>44905</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45950</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>45949</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>45949</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>45948</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>46155</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45949</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>46155</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>45904</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>45755</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45482</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>46155</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>45358</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>44631</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45960</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45960</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>45138</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>45691</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -38087,7 +38087,7 @@
         <v>44943</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>44796</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>44586</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45966</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>45384</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>45966</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>45093</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>44973</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         <v>46163</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>46163</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45076</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>45096</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45394</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45054</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45978</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>45007</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>45978</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>45568</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39416,7 +39416,7 @@
         <v>45978</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>45978</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>46163</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>44993</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39718,7 +39718,7 @@
         <v>45985</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
         <v>44732</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>44655</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>45197</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>45194</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>44660</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>45996</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40239,7 +40239,7 @@
         <v>45999</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>46003</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>46008</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>45842</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45123</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44726</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>44598</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>45751</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45762</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>45282</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>45107</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>45259</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>46176</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>46176</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>45621</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>44775</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>46176</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>44523</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>46176</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>46176</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>46176</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45740</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>46040</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>44981</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>44803</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>46043</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>46043</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>44596</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>46048</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42396,7 +42396,7 @@
         <v>46181</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>46050</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>45082</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         <v>44972</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>46182</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45047</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>44952</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>44775</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -43000,7 +43000,7 @@
         <v>46183</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>46183</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>46065</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>46064</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43297,7 +43297,7 @@
         <v>46064</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>46065</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>46184</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45154</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43594,7 +43594,7 @@
         <v>44938</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43667,7 +43667,7 @@
         <v>45114</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>46072</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>45090</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>44525</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>44512</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>44890</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>46087</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>46087</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44281,7 +44281,7 @@
         <v>46087</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44359,7 +44359,7 @@
         <v>44895</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>44908</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44510,7 +44510,7 @@
         <v>46057</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44583,7 +44583,7 @@
         <v>44973</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>45702</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>44553</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45680</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>46098</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>44874</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>46196</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -45119,7 +45119,7 @@
         <v>46195</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -45197,7 +45197,7 @@
         <v>44515</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45170</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>46104</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45421,7 +45421,7 @@
         <v>46106</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>45012</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>46108</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>45202</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>44586</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>46108</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>46112</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>46112</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>46111</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>46112</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>46112</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>46113</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>46113</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>45462</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>46199</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45005</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>44715</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45195</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>46200</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46833,7 +46833,7 @@
         <v>44609</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>46200</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>44523</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -47057,7 +47057,7 @@
         <v>44660</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>44684</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -47208,7 +47208,7 @@
         <v>46199</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>46200</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -47364,7 +47364,7 @@
         <v>44602</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>44916</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47515,7 +47515,7 @@
         <v>46134</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         <v>46134</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>44978</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45796</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>44739</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45040</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>45203</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -48051,7 +48051,7 @@
         <v>45819</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         <v>45233</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>45225</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45778</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>45835</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>45812</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48504,7 +48504,7 @@
         <v>46136</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>44805</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>46206</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48728,7 +48728,7 @@
         <v>44501</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>46206</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48879,7 +48879,7 @@
         <v>46206</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>46209</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45617</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>46209</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>45476</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -49254,7 +49254,7 @@
         <v>46209</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>46209</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>46209</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>46209</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>46211</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>45560</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>46211</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>44665</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>45142</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49946,7 +49946,7 @@
         <v>45076</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>46217</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>46217</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>46219</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>46219</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>46181</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>46219</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>45072</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>44591</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50628,7 +50628,7 @@
         <v>45455</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50706,7 +50706,7 @@
         <v>46063</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50779,7 +50779,7 @@
         <v>45089</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>46274</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>44909</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>46274</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -51081,7 +51081,7 @@
         <v>46274</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>46274</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -51237,7 +51237,7 @@
         <v>44824</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
         <v>44890</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>46279</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>46276</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         <v>44923</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>46276</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>44977</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51783,7 +51783,7 @@
         <v>44795</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>46281</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51939,7 +51939,7 @@
         <v>46281</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45621</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45621</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45621</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>46239</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>46239</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -52407,7 +52407,7 @@
         <v>46240</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>46282</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -52558,7 +52558,7 @@
         <v>44949</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52631,7 +52631,7 @@
         <v>46240</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>46240</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52787,7 +52787,7 @@
         <v>46240</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52865,7 +52865,7 @@
         <v>45176</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52938,7 +52938,7 @@
         <v>45740</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>44998</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         <v>44522</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -53157,7 +53157,7 @@
         <v>46241</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -53235,7 +53235,7 @@
         <v>44536</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -53308,7 +53308,7 @@
         <v>44578</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -53381,7 +53381,7 @@
         <v>46287</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -53454,7 +53454,7 @@
         <v>46286</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -53527,7 +53527,7 @@
         <v>45213</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53600,7 +53600,7 @@
         <v>44810</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53673,7 +53673,7 @@
         <v>46246</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53751,7 +53751,7 @@
         <v>46245</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53829,7 +53829,7 @@
         <v>45259</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53902,7 +53902,7 @@
         <v>46246</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53980,7 +53980,7 @@
         <v>46289</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>44841</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -54126,7 +54126,7 @@
         <v>44550</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -54199,7 +54199,7 @@
         <v>45337</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -54272,7 +54272,7 @@
         <v>44923</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -54350,7 +54350,7 @@
         <v>46293</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -54428,7 +54428,7 @@
         <v>46290</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -54501,7 +54501,7 @@
         <v>45225</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54574,7 +54574,7 @@
         <v>44953</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>44552</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54720,7 +54720,7 @@
         <v>45467</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>45147</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
         <v>44783</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>44973</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55027,7 +55027,7 @@
         <v>46252</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55105,7 +55105,7 @@
         <v>44972</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>45687</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -55256,7 +55256,7 @@
         <v>46056</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -55334,7 +55334,7 @@
         <v>44725</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -55407,7 +55407,7 @@
         <v>45040</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -55480,7 +55480,7 @@
         <v>44915</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -55553,7 +55553,7 @@
         <v>45097</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55626,7 +55626,7 @@
         <v>44531</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55704,7 +55704,7 @@
         <v>46279</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55782,7 +55782,7 @@
         <v>46253</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55855,7 +55855,7 @@
         <v>45468</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>46056</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56006,7 +56006,7 @@
         <v>46300</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>44496</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>46258</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -56235,7 +56235,7 @@
         <v>45813</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -56313,7 +56313,7 @@
         <v>44938</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -56386,7 +56386,7 @@
         <v>46300</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -56464,7 +56464,7 @@
         <v>46300</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>46300</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>45597</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56693,7 +56693,7 @@
         <v>46181</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>46043</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56844,7 +56844,7 @@
         <v>46176</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56917,7 +56917,7 @@
         <v>45562</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56995,7 +56995,7 @@
         <v>46258</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57073,7 +57073,7 @@
         <v>46258</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -57151,7 +57151,7 @@
         <v>46178</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>46300</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>46300</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>45538</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45520</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -57536,7 +57536,7 @@
         <v>45569</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         <v>45013</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57682,7 +57682,7 @@
         <v>45546</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>45569</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57833,7 +57833,7 @@
         <v>45574</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57906,7 +57906,7 @@
         <v>45572</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57979,7 +57979,7 @@
         <v>44598</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45569</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58130,7 +58130,7 @@
         <v>46199</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>45572</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -58276,7 +58276,7 @@
         <v>45253</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -58349,7 +58349,7 @@
         <v>46258</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>46259</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -58505,7 +58505,7 @@
         <v>46260</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -58583,7 +58583,7 @@
         <v>46304</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58661,7 +58661,7 @@
         <v>46304</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58739,7 +58739,7 @@
         <v>45670</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58812,7 +58812,7 @@
         <v>45499</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58890,7 +58890,7 @@
         <v>45456</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58968,7 +58968,7 @@
         <v>45797</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59041,7 +59041,7 @@
         <v>46154</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59119,7 +59119,7 @@
         <v>46156</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>46262</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -59275,7 +59275,7 @@
         <v>46219</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -59348,7 +59348,7 @@
         <v>45931</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -59421,7 +59421,7 @@
         <v>45813</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -59499,7 +59499,7 @@
         <v>46245</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>45734</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59650,7 +59650,7 @@
         <v>45524</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59723,7 +59723,7 @@
         <v>46266</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59796,7 +59796,7 @@
         <v>45749</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59874,7 +59874,7 @@
         <v>46266</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59952,7 +59952,7 @@
         <v>45740</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60025,7 +60025,7 @@
         <v>46309</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60098,7 +60098,7 @@
         <v>45632</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60171,7 +60171,7 @@
         <v>46309</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45805</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -60317,7 +60317,7 @@
         <v>46309</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45811</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -60468,7 +60468,7 @@
         <v>45812</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -60541,7 +60541,7 @@
         <v>46267</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -60619,7 +60619,7 @@
         <v>45817</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60697,7 +60697,7 @@
         <v>46289</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60770,7 +60770,7 @@
         <v>45708</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60848,7 +60848,7 @@
         <v>45813</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60926,7 +60926,7 @@
         <v>46311</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60999,7 +60999,7 @@
         <v>45824</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61072,7 +61072,7 @@
         <v>45831</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61145,7 +61145,7 @@
         <v>45830</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>45830</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -61291,7 +61291,7 @@
         <v>45833</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>45807</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45842</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -61510,7 +61510,7 @@
         <v>45467</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -61583,7 +61583,7 @@
         <v>45719</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61656,7 +61656,7 @@
         <v>45770</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61734,7 +61734,7 @@
         <v>45759</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61807,7 +61807,7 @@
         <v>45869</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61880,7 +61880,7 @@
         <v>44970</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>44964</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62026,7 +62026,7 @@
         <v>45078</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62099,7 +62099,7 @@
         <v>45428</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62172,7 +62172,7 @@
         <v>45428</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>44729</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -62323,7 +62323,7 @@
         <v>45390</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -62401,7 +62401,7 @@
         <v>44672</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -62474,7 +62474,7 @@
         <v>45182</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -62552,7 +62552,7 @@
         <v>45916</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62625,7 +62625,7 @@
         <v>45957</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62698,7 +62698,7 @@
         <v>46034</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62776,7 +62776,7 @@
         <v>46089</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62854,7 +62854,7 @@
         <v>46296</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>46204</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>45114</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45106</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>46132</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>46196</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>45659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>45590</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>45061</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>45660</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>43955</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>46132</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45439</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>46030</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>46183</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45106</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>46279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45182</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>46205</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>44918</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>46009</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>46132</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>45210</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>44865</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44662</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>45660</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45622</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>44938</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>45076</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>45947</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44771</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45190</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>46205</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>44935</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45796</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>44644</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45226</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>45891</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>44194</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45076</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>44636</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>46170</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>45840</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>44837</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>45362</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45520</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45198</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45160</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>44588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44779</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44739</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>45238</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>44727</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>46132</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45205</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>44819</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>44511</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44684</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>44874</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>44728</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45078</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44525</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>45107</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>45412</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>46265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>45315</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>45070</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>44984</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>45999</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>46048</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>44858</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>45545</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>45699</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45390</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44874</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>45372</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>44903</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>46161</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45999</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>46121</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>44683</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>44729</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>45446</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>46282</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45460</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45274</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>45895</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>46089</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>44495</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>44515</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>44578</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>44778</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45068</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45045</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45425</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45583</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>45775</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>46142</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44644</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45951</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>46001</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>45743</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>45063</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44883</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45063</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>46287</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>46252</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>46300</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45393</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>44782</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>44859</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44687</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>44813</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>44622</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44501</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>44792</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>44715</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>44606</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>45154</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>45678</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45329</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>45896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45831</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>44985</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>46139</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45695</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44607</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44712</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>46154</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45384</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>45160</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>45436</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>44915</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>45013</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>46056</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>46062</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>44572</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>44991</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44875</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45162</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>46098</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>46195</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>46195</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>45156</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>46063</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>45387</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>44979</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>44998</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>46211</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>44517</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>46002</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>45135</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>46275</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>46235</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>45078</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>45250</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>46290</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45007</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>45213</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>45513</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>44509</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>46259</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>46260</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>46268</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45078</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45218</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45178</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>45007</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>44726</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>44491</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>45078</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44610</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45820</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45728</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>46112</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>46191</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>44732</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>44614</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>44729</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>44622</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44501</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>44622</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>44687</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>44664</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>44651</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44644</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>44555</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>44868</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44498</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>44491</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>44838</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>44691</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>44577</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>44661</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>44525</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44649</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>44622</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44613</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44588</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44725</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>44725</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44852</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>44519</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>44598</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>44692</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>44691</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>44694</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>44659</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44715</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>44865</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>44664</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>44757</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44861</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44873</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>44661</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44501</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>44809</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>44809</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>44813</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>44810</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>44635</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44712</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>44669</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>44687</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>44728</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>44608</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>44872</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>44770</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>44739</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>44620</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>44635</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>44687</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>44676</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>44643</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44669</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>44809</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>44576</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>45114</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>44560</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45208</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>44775</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45107</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45621</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45271</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>44991</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44591</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>45054</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44755</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>44783</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45212</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>45110</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>45191</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>44915</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>44651</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>44643</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>44599</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>44599</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>44706</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44651</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>45250</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>44768</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45146</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44860</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45230</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>44987</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>44814</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45670</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45162</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44963</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>45257</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -28166,7 +28166,7 @@
         <v>44746</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>45194</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -28317,7 +28317,7 @@
         <v>45212</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -28395,7 +28395,7 @@
         <v>45530</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44991</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45516</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>44511</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>45063</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45561</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45455</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44533</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>44515</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>45337</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         <v>44555</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>45544</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45462</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44572</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>44770</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>44560</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45419</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>44953</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>44970</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45152</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>45093</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>45379</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45358</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>45520</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>45075</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -30290,7 +30290,7 @@
         <v>45757</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>44643</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>44664</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>44613</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45384</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45520</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>44613</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45225</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45148</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45244</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45102</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>45102</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>44894</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>45341</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>46139</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>45337</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>46139</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45975</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>44496</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45572</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>46034</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45202</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>46034</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44963</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>44874</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>46136</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>44896</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32286,7 +32286,7 @@
         <v>44896</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>45805</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45760</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45895</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45895</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>45895</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45895</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>45187</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45895</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44512</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>45733</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>45840</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>45898</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45102</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>46104</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>46141</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>45233</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>46141</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>46104</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33718,7 +33718,7 @@
         <v>45516</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>45797</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45797</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
         <v>45797</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>44959</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>44991</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -34171,7 +34171,7 @@
         <v>45817</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>44495</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45909</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44950</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45079</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>45519</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>45063</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>44725</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>45433</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>44928</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>44928</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>45621</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>45520</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>46147</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45924</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>45112</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45646</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>45931</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>46153</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         <v>44687</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45362</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>45937</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45102</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>45496</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44591</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45230</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>46155</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45174</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>45040</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>45090</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>45947</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45218</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45239</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>45044</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>44905</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45950</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>45949</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>45949</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>45948</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>46155</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45949</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>46155</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>45904</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>45755</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45482</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>46155</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>45358</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>44631</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45960</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45960</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>45138</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>45691</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -38087,7 +38087,7 @@
         <v>44943</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>44796</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>44586</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45966</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>45384</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>45966</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>45093</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>44973</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         <v>46163</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>46163</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45076</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>45096</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45394</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45054</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45978</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>45007</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>45978</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>45568</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39416,7 +39416,7 @@
         <v>45978</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>45978</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>46163</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>44993</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39718,7 +39718,7 @@
         <v>45985</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
         <v>44732</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>44655</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>45197</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>45194</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>44660</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>45996</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40239,7 +40239,7 @@
         <v>45999</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>46003</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>46008</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>45842</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45123</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44726</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>44598</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>45751</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45762</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>45282</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>45107</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>45259</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>46176</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>46176</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>45621</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>44775</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>46176</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>44523</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>46176</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>46176</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>46176</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45740</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>46040</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>44981</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>44803</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>46043</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>46043</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>44596</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>46048</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42396,7 +42396,7 @@
         <v>46181</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>46050</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>45082</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         <v>44972</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>46182</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45047</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>44952</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>44775</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -43000,7 +43000,7 @@
         <v>46183</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>46183</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>46065</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>46064</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43297,7 +43297,7 @@
         <v>46064</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>46065</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>46184</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45154</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43594,7 +43594,7 @@
         <v>44938</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43667,7 +43667,7 @@
         <v>45114</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>46072</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>45090</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>44525</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>44512</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>44890</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>46087</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>46087</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44281,7 +44281,7 @@
         <v>46087</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44359,7 +44359,7 @@
         <v>44895</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>44908</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44510,7 +44510,7 @@
         <v>46057</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44583,7 +44583,7 @@
         <v>44973</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>45702</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>44553</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45680</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>46098</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>44874</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>46196</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -45119,7 +45119,7 @@
         <v>46195</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -45197,7 +45197,7 @@
         <v>44515</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45170</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>46104</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45421,7 +45421,7 @@
         <v>46106</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>45012</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>46108</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>45202</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>44586</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>46108</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>46112</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>46112</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>46111</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>46112</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>46112</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>46113</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>46113</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>45462</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>46199</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45005</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>44715</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45195</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>46200</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46833,7 +46833,7 @@
         <v>44609</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>46200</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>44523</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -47057,7 +47057,7 @@
         <v>44660</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>44684</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -47208,7 +47208,7 @@
         <v>46199</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>46200</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -47364,7 +47364,7 @@
         <v>44602</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>44916</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47515,7 +47515,7 @@
         <v>46134</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         <v>46134</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>44978</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45796</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>44739</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45040</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>45203</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -48051,7 +48051,7 @@
         <v>45819</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         <v>45233</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>45225</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45778</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>45835</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>45812</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48504,7 +48504,7 @@
         <v>46136</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>44805</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>46206</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48728,7 +48728,7 @@
         <v>44501</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>46206</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48879,7 +48879,7 @@
         <v>46206</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>46209</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45617</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>46209</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>45476</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -49254,7 +49254,7 @@
         <v>46209</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>46209</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>46209</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>46209</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>46211</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>45560</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>46211</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>44665</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>45142</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49946,7 +49946,7 @@
         <v>45076</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>46217</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>46217</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>46219</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>46219</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>46181</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>46219</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>45072</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>44591</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50628,7 +50628,7 @@
         <v>45455</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50706,7 +50706,7 @@
         <v>46063</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50779,7 +50779,7 @@
         <v>45089</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>46274</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>44909</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>46274</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -51081,7 +51081,7 @@
         <v>46274</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>46274</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -51237,7 +51237,7 @@
         <v>44824</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
         <v>44890</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>46279</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>46276</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         <v>44923</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>46276</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>44977</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51783,7 +51783,7 @@
         <v>44795</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>46281</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51939,7 +51939,7 @@
         <v>46281</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45621</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45621</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45621</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>46239</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>46239</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -52407,7 +52407,7 @@
         <v>46240</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>46282</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -52558,7 +52558,7 @@
         <v>44949</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52631,7 +52631,7 @@
         <v>46240</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>46240</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52787,7 +52787,7 @@
         <v>46240</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52865,7 +52865,7 @@
         <v>45176</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52938,7 +52938,7 @@
         <v>45740</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>44998</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         <v>44522</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -53157,7 +53157,7 @@
         <v>46241</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -53235,7 +53235,7 @@
         <v>44536</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -53308,7 +53308,7 @@
         <v>44578</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -53381,7 +53381,7 @@
         <v>46287</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -53454,7 +53454,7 @@
         <v>46286</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -53527,7 +53527,7 @@
         <v>45213</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53600,7 +53600,7 @@
         <v>44810</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53673,7 +53673,7 @@
         <v>46246</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53751,7 +53751,7 @@
         <v>46245</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53829,7 +53829,7 @@
         <v>45259</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53902,7 +53902,7 @@
         <v>46246</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53980,7 +53980,7 @@
         <v>46289</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>44841</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -54126,7 +54126,7 @@
         <v>44550</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -54199,7 +54199,7 @@
         <v>45337</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -54272,7 +54272,7 @@
         <v>44923</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -54350,7 +54350,7 @@
         <v>46293</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -54428,7 +54428,7 @@
         <v>46290</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -54501,7 +54501,7 @@
         <v>45225</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54574,7 +54574,7 @@
         <v>44953</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>44552</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54720,7 +54720,7 @@
         <v>45467</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>45147</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
         <v>44783</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>44973</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -55027,7 +55027,7 @@
         <v>46252</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -55105,7 +55105,7 @@
         <v>44972</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>45687</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -55256,7 +55256,7 @@
         <v>46056</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -55334,7 +55334,7 @@
         <v>44725</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -55407,7 +55407,7 @@
         <v>45040</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -55480,7 +55480,7 @@
         <v>44915</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -55553,7 +55553,7 @@
         <v>45097</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55626,7 +55626,7 @@
         <v>44531</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55704,7 +55704,7 @@
         <v>46279</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55782,7 +55782,7 @@
         <v>46253</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55855,7 +55855,7 @@
         <v>45468</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>46056</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -56006,7 +56006,7 @@
         <v>46300</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>44496</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>46258</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -56235,7 +56235,7 @@
         <v>45813</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -56313,7 +56313,7 @@
         <v>44938</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -56386,7 +56386,7 @@
         <v>46300</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -56464,7 +56464,7 @@
         <v>46300</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>46300</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>45597</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56693,7 +56693,7 @@
         <v>46181</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>46043</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56844,7 +56844,7 @@
         <v>46176</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56917,7 +56917,7 @@
         <v>45562</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56995,7 +56995,7 @@
         <v>46258</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -57073,7 +57073,7 @@
         <v>46258</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -57151,7 +57151,7 @@
         <v>46178</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>46300</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>46300</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>45538</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45520</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -57536,7 +57536,7 @@
         <v>45569</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         <v>45013</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57682,7 +57682,7 @@
         <v>45546</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>45569</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57833,7 +57833,7 @@
         <v>45574</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57906,7 +57906,7 @@
         <v>45572</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57979,7 +57979,7 @@
         <v>44598</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45569</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -58130,7 +58130,7 @@
         <v>46199</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>45572</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -58276,7 +58276,7 @@
         <v>45253</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -58349,7 +58349,7 @@
         <v>46258</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>46259</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -58505,7 +58505,7 @@
         <v>46260</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -58583,7 +58583,7 @@
         <v>46304</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58661,7 +58661,7 @@
         <v>46304</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58739,7 +58739,7 @@
         <v>45670</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58812,7 +58812,7 @@
         <v>45499</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58890,7 +58890,7 @@
         <v>45456</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58968,7 +58968,7 @@
         <v>45797</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -59041,7 +59041,7 @@
         <v>46154</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -59119,7 +59119,7 @@
         <v>46156</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>46262</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -59275,7 +59275,7 @@
         <v>46219</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -59348,7 +59348,7 @@
         <v>45931</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -59421,7 +59421,7 @@
         <v>45813</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -59499,7 +59499,7 @@
         <v>46245</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>45734</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59650,7 +59650,7 @@
         <v>45524</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59723,7 +59723,7 @@
         <v>46266</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59796,7 +59796,7 @@
         <v>45749</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59874,7 +59874,7 @@
         <v>46266</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59952,7 +59952,7 @@
         <v>45740</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -60025,7 +60025,7 @@
         <v>46309</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -60098,7 +60098,7 @@
         <v>45632</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -60171,7 +60171,7 @@
         <v>46309</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45805</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -60317,7 +60317,7 @@
         <v>46309</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45811</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -60468,7 +60468,7 @@
         <v>45812</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -60541,7 +60541,7 @@
         <v>46267</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -60619,7 +60619,7 @@
         <v>45817</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60697,7 +60697,7 @@
         <v>46289</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60770,7 +60770,7 @@
         <v>45708</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60848,7 +60848,7 @@
         <v>45813</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60926,7 +60926,7 @@
         <v>46311</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60999,7 +60999,7 @@
         <v>45824</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -61072,7 +61072,7 @@
         <v>45831</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -61145,7 +61145,7 @@
         <v>45830</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>45830</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -61291,7 +61291,7 @@
         <v>45833</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>45807</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45842</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -61510,7 +61510,7 @@
         <v>45467</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -61583,7 +61583,7 @@
         <v>45719</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61656,7 +61656,7 @@
         <v>45770</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61734,7 +61734,7 @@
         <v>45759</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61807,7 +61807,7 @@
         <v>45869</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61880,7 +61880,7 @@
         <v>44970</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>44964</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -62026,7 +62026,7 @@
         <v>45078</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -62099,7 +62099,7 @@
         <v>45428</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -62172,7 +62172,7 @@
         <v>45428</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>44729</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -62323,7 +62323,7 @@
         <v>45390</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -62401,7 +62401,7 @@
         <v>44672</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -62474,7 +62474,7 @@
         <v>45182</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -62552,7 +62552,7 @@
         <v>45916</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62625,7 +62625,7 @@
         <v>45957</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62698,7 +62698,7 @@
         <v>46034</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62776,7 +62776,7 @@
         <v>46089</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62854,7 +62854,7 @@
         <v>46296</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
